--- a/leads/voice-agent-leads-2026-09.xlsx
+++ b/leads/voice-agent-leads-2026-09.xlsx
@@ -8,12 +8,14 @@
   </bookViews>
   <sheets>
     <sheet name="Sıcak Lead (doğrulanmış)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Tüm Liste (255)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Nasıl kullanılır" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Karar Vericiler (LinkedIn)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Tüm Liste (255)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Nasıl kullanılır" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sıcak Lead (doğrulanmış)'!$A$1:$S$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tüm Liste (255)'!$A$1:$O$256</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Karar Vericiler (LinkedIn)'!$A$1:$O$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tüm Liste (255)'!$A$1:$O$256</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -73,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -86,6 +88,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -451,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S18"/>
+  <dimension ref="A1:T18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -473,6 +476,7 @@
     <col width="28" customWidth="1" min="17" max="17"/>
     <col width="60" customWidth="1" min="18" max="18"/>
     <col width="30" customWidth="1" min="19" max="19"/>
+    <col width="45" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -571,6 +575,11 @@
           <t>maps linki</t>
         </is>
       </c>
+      <c r="T1" s="6" t="inlineStr">
+        <is>
+          <t>karar verici (LinkedIn)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -603,8 +612,6 @@
           <t>+90 850 850 1276</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>info@dentco.net, info@yesilyurtdent.com.tr</t>
@@ -658,6 +665,7 @@
           <t>https://www.google.com/maps/search/?api=1&amp;query=%C3%96zel%20Ye%C5%9Filyurt%20A%C4%9F%C4%B1z%20Ve%20Di%C5%9F%20Sa%C4%9Fl%C4%B1%C4%9F%C4%B1%20Poliklini%C4%9Fi&amp;query_place_id=ChIJiRIPFczeuxQRj5LdbU3EKLw</t>
         </is>
       </c>
+      <c r="T2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -753,6 +761,11 @@
           <t>https://www.google.com/maps/search/?api=1&amp;query=Yal%C4%B1%20A%C4%9F%C4%B1z%20ve%20Di%C5%9F%20Sa%C4%9Fl%C4%B1%C4%9F%C4%B1%20Poliklini%C4%9Fi&amp;query_place_id=ChIJMzF3EV_duxQRPBYJ-cMuBIk</t>
         </is>
       </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>Dicle Koçyiğit (Klinik / Operasyon müdürü) — dicle.kocyigit@yalidis.com; Ilgın Gözde Ketancı (Pazarlama) — ilgin.ketanci@yalidis.com</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -785,11 +798,6 @@
           <t>+90 544 943 95 99</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>4.6</t>
@@ -828,6 +836,7 @@
           <t>https://www.google.com/maps/search/?api=1&amp;query=Retina%20A%C4%9F%C4%B1z%20ve%20Di%C5%9F%20Sa%C4%9Fl%C4%B1%C4%9F%C4%B1%20Poliklini%C4%9Fi&amp;query_place_id=ChIJRSXduT63yhQR6o5kBfLdLgs</t>
         </is>
       </c>
+      <c r="T4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -865,13 +874,11 @@
           <t>902423227834</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>info@ecedent.com.tr</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>https://www.ecedent.com.tr/</t>
@@ -915,6 +922,11 @@
           <t>https://www.google.com/maps/search/?api=1&amp;query=%C3%96zel%20Ece%20A%C4%9F%C4%B1z%20Di%C5%9F%20Sa%C4%9Fl%C4%B1%C4%9F%C4%B1%20Poliklini%C4%9Fi&amp;query_place_id=ChIJheg6sDaFwxQR-_ocbKQ6Bp0</t>
         </is>
       </c>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>Gülnaz Başbunar (Çalışan (unvan yok)) — gulnaz.basbunar@ecedent.com.tr</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -952,7 +964,6 @@
           <t>905526595155</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>bilgi@ilkedis.com</t>
@@ -1006,6 +1017,11 @@
           <t>https://www.google.com/maps/search/?api=1&amp;query=%C3%96zel%20%C4%B0lke%20A%C4%9F%C4%B1z%20ve%20Di%C5%9F%20Sa%C4%9Fl%C4%B1%C4%9F%C4%B1%20Poliklini%C4%9Fi&amp;query_place_id=ChIJiZnf6ijZuxQRgZyAsCUpELw</t>
         </is>
       </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>Barış Portakal (Hekim (klinik)) — baris.portakal@ilkedis.com</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1048,8 +1064,6 @@
           <t>cemalfiratmd@gmail.com</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>https://cemalfiratmd.com/</t>
@@ -1093,6 +1107,7 @@
           <t>https://www.google.com/maps/search/?api=1&amp;query=Prof.%20Dr.%20Cemal%20F%C4%B1rat%20Estetik%20ve%20Plastik%20Cerrahi%20Klini%C4%9Fi&amp;query_place_id=ChIJb9C8uYc3dkAR2lwa1WSPDag</t>
         </is>
       </c>
+      <c r="T7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1125,11 +1140,6 @@
           <t>+90 850 307 1900</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>3.2</t>
@@ -1168,6 +1178,7 @@
           <t>https://www.google.com/maps/search/?api=1&amp;query=%C3%96zel%20EstetikMed%20Poliklini%C4%9Fi&amp;query_place_id=ChIJebxfZ0m7yhQR0sUx9CJtY8U</t>
         </is>
       </c>
+      <c r="T8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1200,10 +1211,6 @@
           <t>+90 212 417 20 17</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>http://www.nuresteguzellik.com/</t>
@@ -1247,6 +1254,7 @@
           <t>https://www.google.com/maps/search/?api=1&amp;query=Nureste%20G%C3%BCzellik%20Fatih&amp;query_place_id=ChIJU0DuSRC7yhQRpJ2UzG1F9R0</t>
         </is>
       </c>
+      <c r="T9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1279,9 +1287,6 @@
           <t>+90 4440987</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>kentdishastanesi</t>
@@ -1330,6 +1335,7 @@
           <t>https://www.google.com/maps/search/?api=1&amp;query=%C4%B0stanbul%20Kent%20%C3%9Cniversitesi%20Di%C5%9F%20Hastanesi&amp;query_place_id=ChIJQW9tr4C3yhQR58olFoa8xoU</t>
         </is>
       </c>
+      <c r="T10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1362,11 +1368,6 @@
           <t>+90 552 797 56 87</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>4.5</t>
@@ -1405,6 +1406,7 @@
           <t>https://www.google.com/maps/search/?api=1&amp;query=Estenbul%20Beauty%20Center%20%7C%20Lazer%20Epilasyon%20ve%20Cilt%20Bak%C4%B1m%C4%B1&amp;query_place_id=ChIJAQGB_3S5yhQRyF2_FG-Sl9s</t>
         </is>
       </c>
+      <c r="T11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1442,8 +1444,6 @@
           <t>905467652151</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>dkklinik</t>
@@ -1492,6 +1492,7 @@
           <t>https://www.google.com/maps/search/?api=1&amp;query=DK%20Klinik%20(Dermatology%20and%20Hair%20Transplant%20Antalya)&amp;query_place_id=ChIJU-Yb15WawxQR3iMrDxnC8T4</t>
         </is>
       </c>
+      <c r="T12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1529,13 +1530,11 @@
           <t>905336786154, 905336786195</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>info@hlcpoliklinigi.com</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>https://www.hlcpoliklinigi.com/</t>
@@ -1579,6 +1578,7 @@
           <t>https://www.google.com/maps/search/?api=1&amp;query=HLC%20Poliklini%C4%9Fi&amp;query_place_id=ChIJGwCvWetP0xQRkrGLemWHLvQ</t>
         </is>
       </c>
+      <c r="T13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1616,8 +1616,6 @@
           <t>905323607744</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>hairlost.tr</t>
@@ -1666,6 +1664,7 @@
           <t>https://www.google.com/maps/search/?api=1&amp;query=Hair%20Lost%20Protez%20Sa%C3%A7%20Merkezi&amp;query_place_id=ChIJ4eWUek2FwxQRqWmYqaFOYUc</t>
         </is>
       </c>
+      <c r="T14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -1703,7 +1702,6 @@
           <t>905068506618</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>info@dentavie.com.tr</t>
@@ -1757,6 +1755,11 @@
           <t>https://www.google.com/maps/search/?api=1&amp;query=Dentavie%20Di%C5%9F%20Klini%C4%9Fi&amp;query_place_id=ChIJs7F6uu23yhQR1i3SbWIJnAo</t>
         </is>
       </c>
+      <c r="T15" s="3" t="inlineStr">
+        <is>
+          <t>Claudette Ghoumrawi (Hasta ilişkileri / Sağlık turizmi); Mustafa Deniz Bıçakçı (Hasta ilişkileri / Sağlık turizmi)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -1794,7 +1797,6 @@
           <t>905538326035</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>info@avrupadent.com.tr</t>
@@ -1848,6 +1850,7 @@
           <t>https://www.google.com/maps/search/?api=1&amp;query=%C3%96zel%20Avrupadent%20Ye%C5%9Filyurt%20A%C4%9F%C4%B1z%20ve%20Di%C5%9F%20Sa%C4%9Fl%C4%B1%C4%9F%C4%B1%20Poliklini%C4%9Fi&amp;query_place_id=ChIJEayq8m_fuxQRUfUf7yQ9nPY</t>
         </is>
       </c>
+      <c r="T16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -1885,7 +1888,6 @@
           <t>905301788080</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>info@novarsacekimi.com</t>
@@ -1939,6 +1941,7 @@
           <t>https://www.google.com/maps/search/?api=1&amp;query=%C4%B0zmir%20Sa%C3%A7%20Ekim%20Poliklini%C4%9Fi%20%7C%20Novar%20Sa%C3%A7%20Ekim%20Merkezi&amp;query_place_id=ChIJB-O9YgZjuRQRvxPeHy0b07Q</t>
         </is>
       </c>
+      <c r="T17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -1971,11 +1974,6 @@
           <t>+90 553 536 41 40</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
           <t>4.9</t>
@@ -2012,6 +2010,11 @@
       <c r="S18" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=Clinique%20312%20%C3%96zel%20A%C4%9F%C4%B1z%20ve%20Di%C5%9F%20Sa%C4%9Fl%C4%B1%C4%9F%C4%B1%20Klini%C4%9Fi&amp;query_place_id=ChIJq00Qz5ZP0xQRbrElFtdv3tA</t>
+        </is>
+      </c>
+      <c r="T18" s="3" t="inlineStr">
+        <is>
+          <t>Çağla Şeşen (Kurucu / Sahip)</t>
         </is>
       </c>
     </row>
@@ -2022,6 +2025,2054 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="32" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>sıcak lead</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>işletme</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>il</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>ilçe</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>rol</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>ad soyad</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>unvan (LinkedIn)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>e-posta (bulunan)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>durum</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>e-posta (tahmini)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>tahmin notu</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>klinik e-postası (site)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>klinik telefonu</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>EVET</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Clinique 312 Özel Ağız ve Diş Sağlığı Kliniği</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Çankaya</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Kurucu / Sahip</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Çağla Şeşen</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Dentist, Orthodontist</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://tr.linkedin.com/in/%C3%A7a%C4%9Fla-%C5%9Fe%C5%9Fen-50086839</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>+90 553 536 41 40</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>EVET</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Yalı Ağız ve Diş Sağlığı Polikliniği</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Karabağlar</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Klinik / Operasyon müdürü</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dicle Koçyiğit</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Operasyon ve Kurumsal İlişkiler Yöneticisi</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://tr.linkedin.com/in/diclekocyigit</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>dicle.kocyigit@yalidis.com</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bulundu — riskli (catch-all alan adı)</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>oslo@dishekimi.com</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>+90 232 224 20 50</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>http://www.yalidis.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>EVET</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dentavie Diş Kliniği</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Beyoğlu</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Hasta ilişkileri / Sağlık turizmi</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Claudette Ghoumrawi</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Patient Coordinator at Dentavie ...</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://tr.linkedin.com/in/claudette-ghoumrawi-bb9591220</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>info@dentavie.com.tr</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>+90 506 850 66 18</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>https://dentavie.com.tr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>EVET</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dentavie Diş Kliniği</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Beyoğlu</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Hasta ilişkileri / Sağlık turizmi</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mustafa Deniz Bıçakçı</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sağlık Turizm Koordinatörü</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://tr.linkedin.com/in/denizbicakci/tr</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>info@dentavie.com.tr</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>+90 506 850 66 18</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>https://dentavie.com.tr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>EVET</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Özel İlke Ağız ve Diş Sağlığı Polikliniği</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Konak</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Hekim (klinik)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Barış Portakal</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Diş Hekimi - Özel İlke Ağız ve Diş Sağlığı Polikliniği</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://tr.linkedin.com/in/bar%C4%B1%C5%9F-portakal-9b8a85347</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>baris.portakal@ilkedis.com</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>tahmin — doğrulanmamış</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>bilgi@ilkedis.com</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>+90 232 255 51 55</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>https://ilkedis.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>EVET</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Yalı Ağız ve Diş Sağlığı Polikliniği</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Karabağlar</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Pazarlama</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ilgın Gözde Ketancı</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Yalı Ağız ve Diş Sağlığı Polikliniği şirketinde Healthcare Content Manager</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://tr.linkedin.com/in/ilgngzde</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>ilgin.ketanci@yalidis.com</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bulundu — riskli (catch-all alan adı)</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>oslo@dishekimi.com</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>+90 232 224 20 50</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>http://www.yalidis.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>EVET</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Özel Ece Ağız Diş Sağlığı Polikliniği</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Antalya</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Muratpaşa</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Çalışan (unvan yok)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gülnaz Başbunar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://tr.linkedin.com/in/g%C3%BClnaz-ba%C5%9Fbunar-a76b38212</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>gulnaz.basbunar@ecedent.com.tr</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>tahmin — doğrulanmamış</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>info@ecedent.com.tr</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>+90 242 322 78 34</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>https://www.ecedent.com.tr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Anka Estetik ve Plastik Cerrahi, Doç.Dr.Anı Çinpolat-Doç.Dr.Gamze Bektaş</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Şişli</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Kurucu / Sahip (klinik adı)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Anı cinpolat</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Plastic surgery at Akdeniz University</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://tr.linkedin.com/in/an%C4%B1-cinpolat-9276061b</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ani.cinpolat@ankaplasticsurgery.com</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>tahmin — doğrulanmamış</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>info@ankaplasticsurgery.com</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>+90 212 296 89 61</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>https://www.ankaplasticsurgery.com/tr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ankara international Saç Ekimi - Doç.Dr.Serdar Gökrem</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Çankaya</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Kurucu / Sahip (klinik adı)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Serdar Gökrem</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Estetik Plastik ve Rekonstrüktif Cerrahi Uzmanı</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://tr.linkedin.com/in/serdar-g%C3%B6krem</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>serdar.gokrem@ankarainternationalsacekimi.com</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>tahmin — doğrulanmamış</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>+90 312 494 05 27</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>https://www.ankarainternationalsacekimi.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Doç Dr Mehmet Tapan , Plastic Surgeon</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Antalya</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Muratpaşa</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Kurucu / Sahip (klinik adı)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mehmet Tapan</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Plastic,Reconstructive and Aesthetic Surgeon, Associate Professor, European Board Certified</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://tr.linkedin.com/in/mehmet-tapan-7844b8158</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>mehmet.tapan@drmehmettapan.com</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>tahmin — doğrulanmamış</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>drmtapan@gmail.com</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>+90 533 376 17 72</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>https://drmehmettapan.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dr Özgür Koldaş Polikliniği- Ankara Botoks, Dolgu, Medikal Estetik, Saç Ekimi</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Çankaya</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Kurucu / Sahip (klinik adı)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dr. A. Özgür Koldaş</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Doktor</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://tr.linkedin.com/in/dr-ozgur-koldas</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ozgur.koldas@ozgurkoldas.com</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>tahmin — doğrulanmamış</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>info@ozgurkoldas.com</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>+90 850 215 1616</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>https://www.ozgurkoldas.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dr. Güngör Kırmızıgül</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Antalya</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Muratpaşa</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Kurucu / Sahip (klinik adı)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dr. Güngör Kırmızıgül</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dr. Güngör Kırmızıgül Klinik</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://tr.linkedin.com/in/dr-g%C3%BCng%C3%B6r-k%C4%B1rm%C4%B1z%C4%B1g%C3%BCl-9566b51a6</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>gungor.kirmizigul@drgungorkirmizigul.com</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>tahmin — doğrulanmamış</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>info@drgungorkirmizigul.com</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>+90 530 159 85 16</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>https://www.drgungorkirmizigul.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dr.Bekir Hucuptan - Medikal Estetik Uygulamalar - Ozon terapi - Mezoterapi</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Narlıdere</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Kurucu / Sahip (klinik adı)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Bekir HUCUPTAN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Medical Doctor | Human-Centered Healthcare | Wellbeing Systems | Patient Experience | Longevity Perspective</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://tr.linkedin.com/in/bekirhucuptan</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>bekir.hucuptan@drbekir.com</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>tahmin — doğrulanmamış</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>bilgi@drbekirhucuptan.com</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>+90 544 323 13 20</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>http://www.drbekir.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Op. Dr. Didem Tanyel</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Çankaya</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Kurucu / Sahip (klinik adı)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Didem Tanyel</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Plastic&amp;Reconstructive Surgeon</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://tr.linkedin.com/in/didem-tanyel-b95021b4</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>didem.tanyel@didemtanyel.com</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>tahmin — doğrulanmamış</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>+90 551 797 00 70</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>http://www.didemtanyel.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Op. Dr. Özgür Sunay</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Konak</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Kurucu / Sahip (klinik adı)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Op. Dr. Özgür Sunay</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Plastic Surgeon</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://tr.linkedin.com/in/op-dr-%C3%B6zg%C3%BCr-sunay-97683627</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>ozgur.sunay@ozgursunay.com</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>tahmin — doğrulanmamış</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>+90 232 290 57 57</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>http://www.ozgursunay.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Uzm. Dr. Cem Akman | Ankara Botoks, Dolgu, Medikal Estetik</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Çankaya</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Kurucu / Sahip (klinik adı)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Uzman Dr. Cem AKMAN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Özel Medisante Polikliniği Yönetim Kurulu Başkanı</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://tr.linkedin.com/in/uzmdrcemakman</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>cem.akman@drcemakman.com</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>tahmin — doğrulanmamış</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>info@drcemakman.com</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>+90 534 540 06 80</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>https://drcemakman.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dnt Klinik Ağız ve Diş Sağlığı</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Antalya</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Kepez</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Kurucu / Sahip</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Görkem Çelebioğlu</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dnt klinik şirketinde Ortak Diş Hekimi</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://tr.linkedin.com/in/g%C3%B6rkem-%C3%A7elebio%C4%9Flu-7350a8217</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>gorkem.celebioglu@dntclinic.com</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>tahmin — doğrulanmamış</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>+90 242 244 32 22</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>https://dntclinic.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Eges Hair Clinic | İzmir Saç Ekim Merkezi</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Bayraklı</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Kurucu / Sahip</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Eges Hair Clinic</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Eges Hair Clinic Saç Ekim Merkezi şirketinde Founder</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://tr.linkedin.com/in/eges-hair-clinic-3a8b66214</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>şirket profili — kişi değil</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>info@egeshairclinic.com</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>+90 542 180 30 50</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>https://egeshairclinic.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>MEDWORLD CLINIC</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Antalya</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Konyaaltı</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Kurucu / Sahip</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Akif Ilker Can</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Medworld Clinic Sağlık Merkezi Kurucu Ortak</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://tr.linkedin.com/in/akif-ilker-can-ab9948325</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>akif.can@medworldclinic.com</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bulundu — riskli (catch-all alan adı)</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>erik.boulard@free.fr</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>+90 549 800 41 05</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>http://www.medworldclinic.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Zesu Estetik</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Bayraklı</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Kurucu / Sahip</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Zeliha Kırmacı</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Zesu Estetik şirketinde İşletme Sahibi</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://tr.linkedin.com/in/zeliha-k%C4%B1rmac%C4%B1-b45561359</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>zeliha.kirmaci@zesuestetik.com</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>tahmin — doğrulanmamış</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>webmaster@zesuestetik.com</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>+90 555 516 80 80</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>https://zesuestetik.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ÖZEL DENTVİSTA AĞIZ VE DİŞ SAĞLIĞI POLİKLİNİĞİ</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Çankaya</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Kurucu / Sahip</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>MUSA KUTLU</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>DİŞ HEKİMİ</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://tr.linkedin.com/in/musa-kutlu-16832926a</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>musa.kutlu@dentvista.com</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>tahmin — doğrulanmamış</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>info@dentvista.com</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>+90 544 438 78 89</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>http://www.dentvista.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>İzmir Saç Ekim Merkezi | Kuzey Hair Clinic</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Konak</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Kurucu / Sahip</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kuzey Mustafaoğlu</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Company Owner - TheNorth Hair Science</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://tr.linkedin.com/in/kuzey-mustafao%C4%9Flu-b38742213</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>kuzey.mustafaoglu@kuzeyclinic.com</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>tahmin — doğrulanmamış</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>kuzeyhairclinic@gmail.com</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>+90 540 199 35 44</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>https://kuzeyclinic.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>İzmir Saç Ekim Merkezi | Loya Clinic | Fue saç ekimi | İzmir saç PRP ve Mezoterapi | Sakal ekimi | Kaş ekimi</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Bayraklı</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Kurucu / Sahip</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Sevcan Keskin</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Loya Clinic şirketinde Müdür</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://tr.linkedin.com/in/sevcan-keskin-a6395439a</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>sevcan.keskin@loyaclinic.com</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>tahmin — doğrulanmamış</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>info@loyaclinic.com</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>+90 533 133 47 80</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>http://www.loyaclinic.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ata Pera Dental Center</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Beyoğlu</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Hasta ilişkileri / Sağlık turizmi</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Can Kucukcay</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Ata Pera Diş Kliniği</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://tr.linkedin.com/in/can-kucukcay-079918170</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>can.kucukcay@atapera.com</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>bulundu — riskli (catch-all alan adı)</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>ataperadisklinigi@gmail.com, patientrelations@atapera.com</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>+90 533 074 07 22</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>https://www.atapera.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>AtkDentpark Clinic Antalya</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Antalya</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Muratpaşa</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Hasta ilişkileri / Sağlık turizmi</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Burak Yiğit Dinçer</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Patient Coordinator</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://tr.linkedin.com/in/burak-yi%C4%9Fit-din%C3%A7er-015320225</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>burak.dincer@atkdentpark.com</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>bulundu — riskli (catch-all alan adı)</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>+90 552 380 38 64</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>https://www.atkdentpark.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>AtkDentpark Clinic Antalya</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Antalya</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Muratpaşa</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Hasta ilişkileri / Sağlık turizmi</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Nazlı Ebru Daşdöğen</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yabancı Hasta Koordinatörü </t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://tr.linkedin.com/in/nazl%C4%B1-ebru-da%C5%9Fd%C3%B6%C4%9Fen-107381105</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>nazli.dasdogen@atkdentpark.com</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>bulundu — riskli (catch-all alan adı)</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>+90 552 380 38 64</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>https://www.atkdentpark.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>MEDWORLD CLINIC</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Antalya</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Konyaaltı</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Hasta ilişkileri / Sağlık turizmi</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Rana Şen</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Health Tourism - Management</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://tr.linkedin.com/in/rana-%C5%9Fen-80a8a6195</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>rana.sen@medworldclinic.com</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>tahmin — doğrulanmamış</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>erik.boulard@free.fr</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>+90 549 800 41 05</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>http://www.medworldclinic.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Estemark</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Eyüpsultan</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Pazarlama</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Sevil Sarymamedogly</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Yurtdışı Satış Pazarlama</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://tr.linkedin.com/in/sevil-sarymamedogly-993554100</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>sevil.sarymamedogly@estemark.com</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>tahmin — doğrulanmamış</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>info@estemark.com</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>+90 531 711 75 69</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>https://estemark.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Forest Klinik | Estetik &amp; Saç Ekimi &amp; Lazer Epilasyon</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ankara</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Çankaya</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Pazarlama</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>AYSU SELMA ULUDAĞ</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Yönetici Asistanı &amp; Fotoğrafçı &amp; Sosyal Medya Yöneticisi</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://tr.linkedin.com/in/aysuludag</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>aysu.uludag@forestklinik.com</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>tahmin — doğrulanmamış</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>bilgi@forestklinik.com</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>+90 312 287 06 99</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>https://www.forestklinik.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Linemed Poliklinik İzmir</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Bornova</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Pazarlama</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Berra Bayındır</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://tr.linkedin.com/in/berra-bay%C4%B1nd%C4%B1r-6a1b7b2a0</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>berra.bayindir@linemed.com.tr</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>tahmin — doğrulanmamış</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>info@linemed.com.tr</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>+90 212 280 19 86</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>https://linemed.com.tr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Özel Dr. Ulusan Polikliniği | Saç Ekimi İzmir</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Bayraklı</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Pazarlama</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Efkan Kökbil</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Dr. Ulusan MedicalHair Clinic , Social Media Manager</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://tr.linkedin.com/in/efkan-k%C3%B6kbil-01b954105</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>efkan.kokbil@ulusanclinic.com</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>tahmin — doğrulanmamış</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>info@ulusanclinic.com</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>https://www.ulusanclinic.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>İzmir Saç Ekim Merkezi | Loya Clinic | Fue saç ekimi | İzmir saç PRP ve Mezoterapi | Sakal ekimi | Kaş ekimi</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Bayraklı</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Pazarlama</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Kaan Yetkin Toprak</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Videographer/Sosyal medya uzmanı</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://tr.linkedin.com/in/kaan-yetkin-toprak-153064246</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>kaan.toprak@loyaclinic.com</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>tahmin — doğrulanmamış</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>info@loyaclinic.com</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>+90 533 133 47 80</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>http://www.loyaclinic.com/</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:O34"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2155,11 +4206,6 @@
           <t>+90 553 536 41 40</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
           <t>4.9</t>
@@ -2215,13 +4261,11 @@
           <t>905336786154, 905336786195</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>info@hlcpoliklinigi.com</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>https://www.hlcpoliklinigi.com/</t>
@@ -2282,8 +4326,6 @@
           <t>905467652151</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>dkklinik</t>
@@ -2349,8 +4391,6 @@
           <t>905323607744</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>hairlost.tr</t>
@@ -2416,13 +4456,11 @@
           <t>902423227834</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>info@ecedent.com.tr</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>https://www.ecedent.com.tr/</t>
@@ -2488,8 +4526,6 @@
           <t>cemalfiratmd@gmail.com</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>https://cemalfiratmd.com/</t>
@@ -2545,10 +4581,6 @@
           <t>+90 212 417 20 17</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>http://www.nuresteguzellik.com/</t>
@@ -2604,11 +4636,6 @@
           <t>+90 850 307 1900</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t>3.2</t>
@@ -2664,7 +4691,6 @@
           <t>905068506618</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>info@dentavie.com.tr</t>
@@ -2730,9 +4756,6 @@
           <t>+90 4440987</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>kentdishastanesi</t>
@@ -2793,11 +4816,6 @@
           <t>+90 552 797 56 87</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
           <t>4.5</t>
@@ -2848,11 +4866,6 @@
           <t>+90 544 943 95 99</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>4.6</t>
@@ -2908,7 +4921,6 @@
           <t>905538326035</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>info@avrupadent.com.tr</t>
@@ -3054,7 +5066,6 @@
           <t>905526595155</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>bilgi@ilkedis.com</t>
@@ -3120,8 +5131,6 @@
           <t>+90 850 850 1276</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>info@dentco.net, info@yesilyurtdent.com.tr</t>
@@ -3192,7 +5201,6 @@
           <t>905301788080</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>info@novarsacekimi.com</t>
@@ -3228,7 +5236,6 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
           <t>Uzm. Dr. M. Fatih SOMUNCU-Botoks-Dudak Dolgusu-Sıvı Yüz Germe - Mezoterapi-Exosome-Buz Lazer-Altın İğne -HIFU-BBL Lazer-Botox</t>
@@ -3264,7 +5271,6 @@
           <t>dr@fatihsomuncu.com, somuncu.fatih@gmail.com</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>drfatihsomuncu</t>
@@ -3295,7 +5301,6 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
           <t>Egemen Güdül Hair Clinic Ankara Saç Ekim Merkezi Ankara</t>
@@ -3321,10 +5326,6 @@
           <t>+90 507 501 16 29</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>https://www.egemengudulsacekim.com/</t>
@@ -3350,7 +5351,6 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
           <t>Op. Dr. Orhan Murat Özdemir - Estetik ve Plastik Cerrah - Ankara</t>
@@ -3386,7 +5386,6 @@
           <t>doktor@orhanmuratozdemir.com.tr</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>orhanmuratozdemir</t>
@@ -3417,7 +5416,6 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
           <t>Data Hair Clinic &amp; Eyyüp Tütüncü Saç Ekim Merkezi</t>
@@ -3448,7 +5446,6 @@
           <t>905527430930</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>info@datahairclinic.com.tr</t>
@@ -3484,7 +5481,6 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
           <t>Ahmet Arslan Hair Transplant Ankara Saç Ekimi</t>
@@ -3515,7 +5511,6 @@
           <t>5320607161, 905307290688</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>iletisim@ahmetarslanhair.com</t>
@@ -3551,7 +5546,6 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
           <t>Dr Özgür Koldaş Polikliniği- Ankara Botoks, Dolgu, Medikal Estetik, Saç Ekimi</t>
@@ -3582,7 +5576,6 @@
           <t>905421149454, 905616142424</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>info@ozgurkoldas.com</t>
@@ -3618,7 +5611,6 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
           <t>Mesen Saç Ekimi Merkezi</t>
@@ -3654,7 +5646,6 @@
           <t>mesensacekimi@gmail.com</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>ankarasacekimi.mesen</t>
@@ -3685,7 +5676,6 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
           <t>Forest Klinik | Estetik &amp; Saç Ekimi &amp; Lazer Epilasyon</t>
@@ -3711,8 +5701,6 @@
           <t>+90 312 287 06 99</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>bilgi@forestklinik.com</t>
@@ -3748,7 +5736,6 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
           <t>Saç Ekim Merkezi | Buğra Erdal ® Hastane Saç Ekimi | Ankara Saç Ekimi PRP Mezoterapi</t>
@@ -3774,9 +5761,6 @@
           <t>+90 542 527 17 66</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>bugraerdal_hair</t>
@@ -3807,7 +5791,6 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
           <t>Medikodent Diş Kliniği</t>
@@ -3833,10 +5816,6 @@
           <t>+90 506 690 01 11</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>http://www.medikodent.com.tr/</t>
@@ -3862,7 +5841,6 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
           <t>HLC Dental Ağız ve Diş Sağlığı Polikliniği</t>
@@ -3893,8 +5871,6 @@
           <t>905377622083, 905379231610</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>hlcdental, hlchealthcaregroup</t>
@@ -3925,7 +5901,6 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
           <t>ÖZEL DENTVİSTA AĞIZ VE DİŞ SAĞLIĞI POLİKLİNİĞİ</t>
@@ -3951,14 +5926,11 @@
           <t>+90 544 438 78 89</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>info@dentvista.com</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>http://www.dentvista.com/</t>
@@ -3984,7 +5956,6 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
           <t>British Esthetic Ankara</t>
@@ -4010,10 +5981,6 @@
           <t>+90 533 710 66 46</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>http://www.britishesthetic.com/</t>
@@ -4039,7 +6006,6 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
           <t>SAÇ EKİMİ NATUREL HAIR</t>
@@ -4065,11 +6031,6 @@
           <t>+90 505 776 42 80</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
           <t>4.8</t>
@@ -4090,7 +6051,6 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
           <t>Özel Dent Dikmen Ağız ve Diş Sağlığı Polikliniği</t>
@@ -4116,10 +6076,6 @@
           <t>+90 554 009 68 00</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>https://www.ozeldentdikmen.com/</t>
@@ -4145,7 +6101,6 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
           <t>Görkem Kazan Saç Ekimi</t>
@@ -4171,9 +6126,6 @@
           <t>+90 541 669 39 70</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>gorkemkazansacekimi, mgorkemkazan</t>
@@ -4204,7 +6156,6 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
           <t>Ankara Saç Ekim Merkezi (Haircente Clinic)</t>
@@ -4235,7 +6186,6 @@
           <t>905324994575</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>info@haircente.com</t>
@@ -4271,7 +6221,6 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
           <t>Dişhekimi Sadık MERAL - Ortodonti Uzmanı &amp; Dişhekimi Y. Emre MERAL - Protetik Diş Tedavisi Uzmanı</t>
@@ -4297,9 +6246,6 @@
           <t>+90 312 467 04 44</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>doktortakvimi</t>
@@ -4330,7 +6276,6 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
           <t>DentRoyal Ağız ve Diş Sağlığı Polikliniği</t>
@@ -4361,9 +6306,6 @@
           <t>905521840242</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
           <t>https://dentroyalclinic.com/</t>
@@ -4389,7 +6331,6 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
           <t>Özel Ankyra Diş Tedavi Merkezi</t>
@@ -4420,8 +6361,6 @@
           <t>905327336065</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>ankyradental</t>
@@ -4452,7 +6391,6 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
           <t>Uzm. Dr. Cem Akman | Ankara Botoks, Dolgu, Medikal Estetik</t>
@@ -4483,7 +6421,6 @@
           <t>905525434545</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>info@drcemakman.com</t>
@@ -4519,7 +6456,6 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
           <t>Özel Ankara HLC Cerrahi Tıp Merkezi</t>
@@ -4550,8 +6486,6 @@
           <t>905336786154</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>hlchealthcaregroup</t>
@@ -4582,7 +6516,6 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
           <t>Nenehatun42 Ağız ve Diş Sağlığı Polikliniği (Diş Hekimi Oya Kılıçoğlu Torun)</t>
@@ -4608,13 +6541,11 @@
           <t>+90 533 136 66 90</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>nenehatun42@gmail.com, nenehatun42klinik@gmail.com</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>nenehatun42</t>
@@ -4645,7 +6576,6 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
           <t>HLC Clinic, Hair Transplant Turkey</t>
@@ -4671,10 +6601,6 @@
           <t>+41 76 569 42 84</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
           <t>https://www.fue-hlc.com/</t>
@@ -4700,7 +6626,6 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
           <t>Doç. Dr. Arda Küçükgüven | Yüz Germe • Rinoplasti • Plastik Cerrahi</t>
@@ -4726,10 +6651,6 @@
           <t>+90 530 881 92 40</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
           <t>http://www.drardakucukguven.com/</t>
@@ -4755,7 +6676,6 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
           <t>Op. Dr. Taner Bahar</t>
@@ -4786,7 +6706,6 @@
           <t>905327468847</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>info@okanmorkoc.com, info@tanerbahar.com, info@tanerbahar.com.tr</t>
@@ -4822,7 +6741,6 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
           <t>Diş Hekimi Rana Kuzu</t>
@@ -4848,14 +6766,11 @@
           <t>+90 312 495 66 33</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>ranakitap@gmail.com</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
           <t>http://www.ranakuzu.com/</t>
@@ -4881,7 +6796,6 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
           <t>MED-DİŞ Özel Ağız-Diş Sağlığı Polikliniği</t>
@@ -4907,10 +6821,6 @@
           <t>+90 312 427 27 24</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
           <t>http://meddis.com.tr/</t>
@@ -4936,7 +6846,6 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
           <t>Hüseyin Örs Saç Ekim</t>
@@ -4962,10 +6871,6 @@
           <t>+90 533 657 35 24</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
           <t>https://huseyinorssacekimi.com/</t>
@@ -4991,7 +6896,6 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
           <t>Özel Klinik 99 Ağız ve Diş Sağlığı Polikliniği | Ankara, Çankaya</t>
@@ -5022,7 +6926,6 @@
           <t>905406406006</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>iletisim@klinik99.com</t>
@@ -5058,7 +6961,6 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
           <t>Estelite Özel Ağız ve Diş Sağlığı Polikliniği</t>
@@ -5089,7 +6991,6 @@
           <t>05452216898, 903124366992</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>info@estelitedentalclinic.com</t>
@@ -5125,7 +7026,6 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
           <t>Atakule Dent Ağız ve Diş Sağlığı Polikliniği</t>
@@ -5151,8 +7051,6 @@
           <t>+90 534 506 33 68</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>info@doktorsitesi.com</t>
@@ -5188,7 +7086,6 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
           <t>Dr. Sevgi Kurtulmaz | Botoks | Dolgu | Lazer Epilasyon | Cilt Gençleştirme | Hydrafacial | Tüy Sarartma | Alexandrite Lazer</t>
@@ -5214,13 +7111,11 @@
           <t>+90 312 438 19 22</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
           <t>skurtulmaz@yahoo.com</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>drsevgikurtulmaz</t>
@@ -5251,7 +7146,6 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
           <t>Op. Dr. Didem Tanyel</t>
@@ -5277,10 +7171,6 @@
           <t>+90 551 797 00 70</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
           <t>http://www.didemtanyel.com/</t>
@@ -5306,7 +7196,6 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
           <t>Dental Clinic Academy Ağız ve Diş Sağlığı Polikliniği</t>
@@ -5332,11 +7221,6 @@
           <t>+90 312 428 86 44</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
           <t>4.9</t>
@@ -5357,7 +7241,6 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
           <t>Dr. Mustafa Ercan Klinik | Ankara Estetik Cerrahi | Göz Kapağı Estetiği | Meme Estetiği | Botoks | Karın Germe | El Cerrahisi</t>
@@ -5383,10 +7266,6 @@
           <t>+90 505 173 65 55</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
           <t>http://www.opdrmustafaercan.com/</t>
@@ -5412,7 +7291,6 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
           <t>Çocuk Diş Hekimi Prof. Dr. Zafer Çehreli</t>
@@ -5438,8 +7316,6 @@
           <t>+90 532 370 75 17</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>bilgi@zafercehreli.com.tr</t>
@@ -5475,7 +7351,6 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
           <t>Dt. Yalçın Erdin Diş Kliniği</t>
@@ -5501,14 +7376,11 @@
           <t>+90 312 468 80 88</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>destek@natro.com</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
           <t>http://www.yalcinerdin.com/</t>
@@ -5534,7 +7406,6 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
           <t>Estera Poliklinik</t>
@@ -5560,11 +7431,6 @@
           <t>+90 312 438 19 22</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
           <t>4.4</t>
@@ -5585,7 +7451,6 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
           <t>Op. Dr. Görkem Dündar | Doğal Burun Estetiği (Rinoplasti) | Kbb Uzmanı Ankara</t>
@@ -5611,7 +7476,6 @@
           <t>+90 537 500 13 87</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
           <t>drgorkemdundar@gmail.com</t>
@@ -5622,7 +7486,6 @@
           <t>info@gorkemdundar.com</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
           <t>http://drgorkemdundar.com/</t>
@@ -5648,7 +7511,6 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
           <t>Liz Hair Clinic (Ankara Saç Ekimi)</t>
@@ -5679,7 +7541,6 @@
           <t>905452407790</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>info@lizhairclinic.com</t>
@@ -5715,7 +7576,6 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
           <t>Mediest Saç Ekimi Merkezi</t>
@@ -5741,11 +7601,6 @@
           <t>+90 535 848 21 43</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
           <t>5</t>
@@ -5766,7 +7621,6 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
           <t>Arpak Sağlık Hizmetleri</t>
@@ -5792,11 +7646,6 @@
           <t>+90 312 467 66 65</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
           <t>4.8</t>
@@ -5817,7 +7666,6 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
           <t>Dr. Eyüp Can Kliniği</t>
@@ -5843,11 +7691,6 @@
           <t>+90 533 037 48 19</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
           <t>5</t>
@@ -5868,7 +7711,6 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
           <t>Ser Hair Center</t>
@@ -5894,13 +7736,11 @@
           <t>+90 542 118 06 78</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
           <t>serhair1@gmail.com</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>ankara_sacekimi</t>
@@ -5931,7 +7771,6 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
           <t>SUAT ÇİÇEK SAÇ EKİMİ</t>
@@ -5957,11 +7796,6 @@
           <t>+90 532 156 56 72</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
           <t>5</t>
@@ -5982,7 +7816,6 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
           <t>Ankara international Saç Ekimi - Doç.Dr.Serdar Gökrem</t>
@@ -6013,8 +7846,6 @@
           <t>905426181010</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>drserdargokrem_sacekimi</t>
@@ -6045,7 +7876,6 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
           <t>Tunalı Saç Ekimi I Ankara Saç ekimi</t>
@@ -6071,11 +7901,6 @@
           <t>+90 561 614 24 24</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
           <t>4.2</t>
@@ -6096,7 +7921,6 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
           <t>Lacrima Güzellik Salonu | Cilt Bakımı Akne (Sivilce, siyah nokta temizleme)</t>
@@ -6122,10 +7946,6 @@
           <t>+90 507 587 78 79</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
           <t>http://lacrimaguzelliksalonu.com/</t>
@@ -6151,7 +7971,6 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
           <t>Dent-in Ankara Ağız ve Diş Sağlığı Polikliniği</t>
@@ -6177,8 +7996,6 @@
           <t>+90 312 439 38 39</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>info@dentinankara.com.tr</t>
@@ -6214,7 +8031,6 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
           <t>Estelifehair Saç Ekimi</t>
@@ -6245,7 +8061,6 @@
           <t>905452732323</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>info@estelifehair.com</t>
@@ -6281,7 +8096,6 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
           <t>Şura Ünal Saç Ekim Uzmanı</t>
@@ -6307,13 +8121,11 @@
           <t>+90 544 822 06 63</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
           <t>suraunal.tr@gmail.com</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>suraunal_hair</t>
@@ -6344,7 +8156,6 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
           <t>Dr. Serkan İlhan | Aesthetic &amp; Plastic Surgery Clinic Antalya</t>
@@ -6375,7 +8186,6 @@
           <t>905054434420</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>info@drserkanilhan.com</t>
@@ -6411,7 +8221,6 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
           <t>S Clinic Antalya - Saç Çoğaltma, Saç Bakım ve Güzellik Merkezi</t>
@@ -6437,9 +8246,6 @@
           <t>+90 553 705 40 95</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>_n, rsrc.php</t>
@@ -6470,7 +8276,6 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
           <t>Op. Dr. Handan Şimşek Turan</t>
@@ -6501,7 +8306,6 @@
           <t>905540070770</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>info@handansimsekturan.com</t>
@@ -6537,7 +8341,6 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
           <t>Hair Transplant Antalya</t>
@@ -6563,10 +8366,6 @@
           <t>+90 554 893 64 79</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
           <t>http://www.hairtransplantantalya.net/</t>
@@ -6592,7 +8391,6 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
           <t>Clinicways</t>
@@ -6623,8 +8421,6 @@
           <t>905422828232</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>clinicways</t>
@@ -6655,7 +8451,6 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
           <t>Op. Dr. Altan Tekin, Estetik ve Plastik Cerrah Antalya</t>
@@ -6681,9 +8476,6 @@
           <t>+90 544 138 84 64</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>draltantekin</t>
@@ -6714,7 +8506,6 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
           <t>Doç. Dr. Asım Uslu Plastik Rekostrüktif ve Estetik Cerrahi</t>
@@ -6750,7 +8541,6 @@
           <t>usluasim@gmail.com</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>docdrasimuslu</t>
@@ -6781,7 +8571,6 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
           <t>MEDWORLD CLINIC</t>
@@ -6852,7 +8641,6 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
           <t>G&amp;F Klinik</t>
@@ -6878,9 +8666,6 @@
           <t>+90 532 516 14 07</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>gfmuayenehane</t>
@@ -6911,7 +8696,6 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
           <t>Palmiye Ağız ve Diş Sağlığı Polikliniği</t>
@@ -6942,13 +8726,11 @@
           <t>905012447007</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>info@palmiyedental.com</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
           <t>http://www.palmiyedis.com/</t>
@@ -6974,7 +8756,6 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
           <t>a-dent Özel Ağız ve Diş Sağlığı Polikliniği</t>
@@ -7005,7 +8786,6 @@
           <t>447470310351, 447584367274</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>info@adentturkey.com</t>
@@ -7041,7 +8821,6 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
           <t>MRV Dental Ağız Ve Diş Sağlığı Polikliniği</t>
@@ -7072,7 +8851,6 @@
           <t>905077472247, 905513800701</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>hello@mrvdental.com, info@mrvdental.com</t>
@@ -7108,7 +8886,6 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
           <t>Op. Dr. Necdet Urhan Estetik Plastik Cerrahi Kliniği</t>
@@ -7134,8 +8911,6 @@
           <t>+90 533 200 26 64</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>info@drnecdeturhan.com</t>
@@ -7171,7 +8946,6 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
           <t>Op. Dr. H. Seçkin Okşar Estetik,Plastik ve Rekonstrüktif Cerrahi Kliniği</t>
@@ -7197,10 +8971,6 @@
           <t>+90 541 514 04 97</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
           <t>http://www.aestheticsurgeryart.com/</t>
@@ -7226,7 +8996,6 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
           <t>Doç Dr Mehmet Tapan , Plastic Surgeon</t>
@@ -7252,13 +9021,11 @@
           <t>+90 533 376 17 72</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
           <t>drmtapan@gmail.com</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>drmehmettapan</t>
@@ -7289,7 +9056,6 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
           <t>Akdeniz Antalya Saç Ekimi - Hair Transplant Antalya</t>
@@ -7360,7 +9126,6 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
           <t>Dr. Güngör Kırmızıgül</t>
@@ -7386,8 +9151,6 @@
           <t>+90 530 159 85 16</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>info@drgungorkirmizigul.com</t>
@@ -7423,7 +9186,6 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
           <t>Haarexclinic Hair Transplant Antalya / Antalya Saç Ekimi</t>
@@ -7454,7 +9216,6 @@
           <t>905320646585, 905522230132</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>info@haarexclinic.com, info@wellfortravel.com, support@gmail.com</t>
@@ -7490,7 +9251,6 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
           <t>Op Dr Gökhan Özerdem, Estetik ve Plastik Cerrah Antalya</t>
@@ -7516,13 +9276,11 @@
           <t>+90 532 370 04 14</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
           <t>gokhanozerdem@gmail.com</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
           <t>opdrgokhanozerdem</t>
@@ -7553,7 +9311,6 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
           <t>IŞILTI Ağız ve Diş Sağlığı Polikliniği</t>
@@ -7579,9 +9336,6 @@
           <t>+90 242 325 35 35</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
           <t>isilti_dental_clinic</t>
@@ -7612,7 +9366,6 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
           <t>Kızılarık Ağız ve Diş Sağlığı Polikliniği</t>
@@ -7638,10 +9391,6 @@
           <t>+90 533 469 07 03</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
           <t>http://www.kizilarikdis.com/</t>
@@ -7667,7 +9416,6 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
           <t>Diş Hekimi Ahmet Kıvanç Göldağ</t>
@@ -7693,8 +9441,6 @@
           <t>+90 551 832 23 97</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>info@doktorsitesi.com</t>
@@ -7730,7 +9476,6 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
           <t>Dnt Klinik Ağız ve Diş Sağlığı</t>
@@ -7756,10 +9501,6 @@
           <t>+90 242 244 32 22</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
           <t>https://dntclinic.com/</t>
@@ -7785,7 +9526,6 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
           <t>ÖZLEM ÖZGÜN ESTETİK GÜZELLİK | Antalya Buz Lazer Epilasyon</t>
@@ -7821,7 +9561,6 @@
           <t>ozlemozgunestetik@gmail.com</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
           <t>ozlem.ozgun.estetik.guzellik</t>
@@ -7852,7 +9591,6 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
           <t>BT Hair Clinic Antalya | Saç Ekimi Merkezi</t>
@@ -7923,7 +9661,6 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
           <t>Prof. Dr. Arzu Akçal Plastik ve Estetik Cerrahi Uzmanı</t>
@@ -7949,10 +9686,6 @@
           <t>+90 532 421 79 74</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
           <t>http://www.arzuakcal.com/tr</t>
@@ -7978,7 +9711,6 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
           <t>klinikeurope</t>
@@ -8014,7 +9746,6 @@
           <t>b@c.com, patientcare@klinikeurope.com</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
           <t>klinikeurope</t>
@@ -8045,7 +9776,6 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
           <t>Özel Mira Ağız ve Diş Sağlığı Polikliniği</t>
@@ -8076,13 +9806,11 @@
           <t>905522330077</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
           <t>info@miraklinik.com</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
         <is>
           <t>http://www.miraklinik.com/</t>
@@ -8108,7 +9836,6 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
           <t>PG Clinics – Hair Transplant Clinic in Antalya</t>
@@ -8134,10 +9861,6 @@
           <t>+90 543 545 69 72</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
           <t>http://www.pgclinics.com/</t>
@@ -8163,7 +9886,6 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
           <t>Doç. Dr. Gülsüm Tetik</t>
@@ -8189,10 +9911,6 @@
           <t>+90 242 502 17 31</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
         <is>
           <t>https://drgulsumtetik.com/</t>
@@ -8218,7 +9936,6 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
           <t>AtkDentpark Clinic Antalya</t>
@@ -8249,8 +9966,6 @@
           <t>905421405301</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
           <t>atkdentpark</t>
@@ -8281,7 +9996,6 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
           <t>Hair Legends | Hair Transplant Antalya</t>
@@ -8307,14 +10021,11 @@
           <t>+90 506 449 70 70</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
           <t>info@antalyahairlegends.com</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
           <t>https://www.antalyahairlegends.com/</t>
@@ -8340,7 +10051,6 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
           <t>Estetik Hair / Antalya Saç Ekimi</t>
@@ -8366,8 +10076,6 @@
           <t>+90 533 655 00 84</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
           <t>info@estetikhair.com</t>
@@ -8403,7 +10111,6 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
           <t>Defne Ağız ve Diş Sağlığı Polikliniği</t>
@@ -8439,7 +10146,6 @@
           <t>defnedispoliklinigi@gmail.com</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
           <t>defnedispoliklinigi</t>
@@ -8470,7 +10176,6 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
           <t>Antalya Medlife Polikliniği</t>
@@ -8496,10 +10201,6 @@
           <t>+90 242 316 35 66</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
           <t>https://antalyamedlife.com/</t>
@@ -8525,7 +10226,6 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
           <t>Doç. Dr. Havva Hilal Ayvaz Çelik</t>
@@ -8551,11 +10251,6 @@
           <t>+90 543 950 59 01</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr">
         <is>
           <t>5</t>
@@ -8576,7 +10271,6 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
           <t>antalya estetik</t>
@@ -8597,12 +10291,6 @@
           <t>Estetik Cerrah</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
         <is>
           <t>4.8</t>
@@ -8623,7 +10311,6 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
           <t>Antalya saç ekimi | Antalya Hair Transplant</t>
@@ -8649,10 +10336,6 @@
           <t>+90 541 876 65 64</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
           <t>https://antalyasacekimi07.com/</t>
@@ -8678,7 +10361,6 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
           <t>Diş Hekimi Ahmet Yılmazer &amp; Oğuz Özbudak</t>
@@ -8704,11 +10386,6 @@
           <t>+90 531 707 42 32</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr">
         <is>
           <t>5</t>
@@ -8729,7 +10406,6 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
           <t>AY-ÇA | Saç Ekimi | Estetik | Lazer Epilasyon Antalya</t>
@@ -8755,10 +10431,6 @@
           <t>+90 242 312 09 37</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
           <t>https://aycapoliklinigi.com/</t>
@@ -8784,7 +10456,6 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
           <t>Tunç Dent Ağız ve Diş Sağlığı Polikliniği (Teeth Veneers Turkey)</t>
@@ -8810,11 +10481,6 @@
           <t>+90 242 326 44 66</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr">
         <is>
           <t>5</t>
@@ -8835,7 +10501,6 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
           <t>DİŞ HEKİMİ MERYEM YILDIZ DİŞ KLİNİĞİ</t>
@@ -8861,11 +10526,6 @@
           <t>+90 505 446 46 10</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr">
         <is>
           <t>5</t>
@@ -8886,7 +10546,6 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
           <t>Novis Hair Clinic</t>
@@ -8917,9 +10576,6 @@
           <t>5010576724</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
           <t>http://novishairclinic.com/</t>
@@ -8945,7 +10601,6 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
           <t>Antalya Hair Transplant Clinic Estevitalya</t>
@@ -8976,7 +10631,6 @@
           <t>905421259940</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
           <t>info@ekoza.com.tr, info@estevitalyahair.com</t>
@@ -9012,7 +10666,6 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
           <t>Clinicana Hair Transplant &amp; Esthetic Surgeries Istanbul Turkey</t>
@@ -9038,8 +10691,6 @@
           <t>+90 549 300 60 69</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
           <t>info@clinicana.com</t>
@@ -9075,7 +10726,6 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
           <t>Ersin Hair Salon / Hairdresser / Hair Extensions Taksim, İstanbul</t>
@@ -9106,7 +10756,6 @@
           <t>905546641010</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
           <t>info@ersincamsari.com</t>
@@ -9142,7 +10791,6 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
           <t>İstanbul Dental Clinic Turkey | Dentist | İmplant | Crowns | Veneers</t>
@@ -9173,8 +10821,6 @@
           <t>905451645177</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
           <t>drkundakcioglu</t>
@@ -9205,7 +10851,6 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
           <t>Dental İmplants Turkey İstanbul Clinic | Best Dental Clinic in Turkey | Best Dentist İstanbul | Turkey Teeth</t>
@@ -9236,7 +10881,6 @@
           <t>905401330000</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
           <t>info@mediax.com, info@turkeydentalimplants.com, info@turkeydentalimplants.net</t>
@@ -9272,7 +10916,6 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
           <t>Queens Nail Studio</t>
@@ -9298,10 +10941,6 @@
           <t>+90 552 522 30 12</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
           <t>http://www.queensnailstudio.com/</t>
@@ -9327,7 +10966,6 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
           <t>Babyface Hair Salon / Hairdresser / Hair Extensions Taksim, İstanbul</t>
@@ -9363,7 +11001,6 @@
           <t>taksimface@gmail.com</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr">
         <is>
           <t>babyfacekuafor</t>
@@ -9394,7 +11031,6 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
           <t>SECRET BEAUTY CENTER / TAKSİM/WAXİNG SALON SKINCARE SALON</t>
@@ -9415,15 +11051,11 @@
           <t>Güzellik Salonu</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr">
         <is>
           <t>tosyaevren@hotmail.com</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
           <t>http://www.secretwomens.online/</t>
@@ -9449,7 +11081,6 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
           <t>BBM Polikliniği</t>
@@ -9480,7 +11111,6 @@
           <t>905330500979</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr">
         <is>
           <t>info@bbmestetik.com</t>
@@ -9516,7 +11146,6 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
           <t>Şule Duyan Beauty Clinic - Hydrafacial / Medical Aesthetic / Laser Hair Removal</t>
@@ -9547,7 +11176,6 @@
           <t>905421082608</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
           <t>info@suleduyanguzellik.com</t>
@@ -9583,7 +11211,6 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
           <t>Diş Hekimi Yahya Terlemez</t>
@@ -9609,8 +11236,6 @@
           <t>+90 212 254 13 98</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
           <t>info@peradental.com</t>
@@ -9646,7 +11271,6 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
           <t>Ata Pera Dental Center</t>
@@ -9672,13 +11296,11 @@
           <t>+90 533 074 07 22</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr">
         <is>
           <t>ataperadisklinigi@gmail.com, patientrelations@atapera.com</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
           <t>ataperadentalcenter, o1</t>
@@ -9709,7 +11331,6 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
           <t>Loyal Dental Taksim</t>
@@ -9740,7 +11361,6 @@
           <t>905010952102</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
           <t>info@loyalclinic.com.tr</t>
@@ -9776,7 +11396,6 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
           <t>Health &amp; Beauty Turkey</t>
@@ -9802,8 +11421,6 @@
           <t>+90 531 596 93 83</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr"/>
-      <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
           <t>info@healthbeautyturkey.com</t>
@@ -9839,7 +11456,6 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
           <t>Perihan Yerşen Güzellik Salonu - Cihangir, Beyoğlu</t>
@@ -9870,8 +11486,6 @@
           <t>905300116173</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr">
         <is>
           <t>perihanyersenguzelliksalonu</t>
@@ -9902,7 +11516,6 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
           <t>Dr. Abdurrahman ÖZTÜRK</t>
@@ -9933,7 +11546,6 @@
           <t>19379935399, 905360630089</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
           <t>info@dr-abdurrahmanozturk.com</t>
@@ -9969,7 +11581,6 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
           <t>Taksim Beauty and Nail Salon &amp; Hairdresser Emsal Doğan International</t>
@@ -10000,8 +11611,6 @@
           <t>905386576962</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
           <t>emsaldogantaksim</t>
@@ -10032,7 +11641,6 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr">
         <is>
           <t>Senamoni - Kadıköy Lazer Epilasyon, Cilt Bakımı ve Leke Tedavileri Merkezi</t>
@@ -10058,10 +11666,6 @@
           <t>+90 216 346 63 46</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr"/>
-      <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
           <t>http://www.senamoniestetik.com/</t>
@@ -10087,7 +11691,6 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
           <t>Pınar Arslan Coiffure &amp; Beauty</t>
@@ -10113,11 +11716,6 @@
           <t>+90 212 252 13 17</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr"/>
-      <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr">
         <is>
           <t>4.8</t>
@@ -10138,7 +11736,6 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr">
         <is>
           <t>Elisa World Güzellik &amp; Bakım</t>
@@ -10164,11 +11761,6 @@
           <t>+90 216 201 10 40</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr"/>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr">
         <is>
           <t>4.6</t>
@@ -10189,7 +11781,6 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
           <t>Diş Hekimi Dr. Dt. Hazar Yaldız</t>
@@ -10215,10 +11806,6 @@
           <t>+90 555 100 42 32</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
           <t>https://drdthazaryaldiz.com/</t>
@@ -10244,7 +11831,6 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr">
         <is>
           <t>زراعة الشعر في تركيا |jawad Medical turkey</t>
@@ -10275,8 +11861,6 @@
           <t>905385606567</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr"/>
-      <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
           <t>jawadmedicalturkey</t>
@@ -10307,7 +11891,6 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
           <t>Hair Transplant Taksim | TESLA TRAVEL ISTANBUL</t>
@@ -10338,9 +11921,6 @@
           <t>905326153523</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr"/>
-      <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
           <t>https://www.hairtransplanttaksim.com/</t>
@@ -10366,7 +11946,6 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr">
         <is>
           <t>Taksim Kuaför ve Güzellik Salonu</t>
@@ -10392,14 +11971,11 @@
           <t>+90 532 277 71 58</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr"/>
-      <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr">
         <is>
           <t>info@taksimkuafor.com</t>
         </is>
       </c>
-      <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr">
         <is>
           <t>https://taksimkuafor.com/</t>
@@ -10425,7 +12001,6 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
           <t>Asya Beauty Lazer Epilasyon Ve Estetik Çapa</t>
@@ -10456,7 +12031,6 @@
           <t>905536396772</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr">
         <is>
           <t>info@asyabeauty.com</t>
@@ -10492,7 +12066,6 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr">
         <is>
           <t>Med-İst Beauty Center | Kadıköy Epilasyon Merkezi ( Lazer Epilasyon, Cilt Bakımı, G5 Masajı, İnci Tozu Leke Bakımı )</t>
@@ -10523,7 +12096,6 @@
           <t>905521641141</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr">
         <is>
           <t>info@medistbeautycenter.com</t>
@@ -10559,7 +12131,6 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr">
         <is>
           <t>Leyla Biçici Beauty I Epilasyon I Bölgesel İncelme I Cilt Bakımı I Zayıflama I Çatlak Onarımı Striort</t>
@@ -10585,10 +12156,6 @@
           <t>+90 543 217 44 40</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr"/>
-      <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr">
         <is>
           <t>http://leylabbeauty.com/</t>
@@ -10614,7 +12181,6 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr">
         <is>
           <t>Estetica Istanbul</t>
@@ -10645,7 +12211,6 @@
           <t>905313007009</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr">
         <is>
           <t>info@esteticaistanbul.com</t>
@@ -10681,7 +12246,6 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr">
         <is>
           <t>May Kuaför 1 | Bay &amp; Bayan Kuaförü</t>
@@ -10707,11 +12271,6 @@
           <t>+90 532 392 50 77</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr"/>
-      <c r="H142" t="inlineStr"/>
-      <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr">
         <is>
           <t>4.5</t>
@@ -10732,7 +12291,6 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
           <t>GalataNo1 Dental</t>
@@ -10763,13 +12321,11 @@
           <t>905535737801</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr">
         <is>
           <t>info@galatano1.com</t>
         </is>
       </c>
-      <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr">
         <is>
           <t>https://galatano1.com/</t>
@@ -10795,7 +12351,6 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
           <t>DRTU | DR. TANSU UZEL Dental Implant, Smile Design &amp; Maxillofacial Surgery Istanbul</t>
@@ -10866,7 +12421,6 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
           <t>DOLU DOLU GÜZELLİK SALONU | FATİH LAZER EPİLASYON | FATİH CİLT BAKIMI</t>
@@ -10892,11 +12446,6 @@
           <t>+90 538 925 66 02</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
-      <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr">
         <is>
           <t>4.8</t>
@@ -10917,7 +12466,6 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
           <t>Dr. Can Aesthetic</t>
@@ -10943,13 +12491,11 @@
           <t>+90 545 440 12 19</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr">
         <is>
           <t>mail.info@drcanesthetic.com.tr</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr">
         <is>
           <t>drcanaesthetic</t>
@@ -10980,7 +12526,6 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
           <t>Seher Tunalı Güzellik Salonu Kadıköy | Microblading , Buz Lazer Epilasyon , Cilt Bakımı</t>
@@ -11051,7 +12596,6 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
           <t>Dr. Cihan Erbay | Kadıköy Medikal Estetik | Dolgu | Botoks | Mezoterapi | Dudak Dolgusu | Gençlik Aşısı</t>
@@ -11077,11 +12621,6 @@
           <t>+90 551 522 00 36</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr">
         <is>
           <t>4.8</t>
@@ -11102,7 +12641,6 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
           <t>ÇİÇEK BEAUTY &amp; NAİL TAKSİM</t>
@@ -11173,7 +12711,6 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
           <t>Haseki Estetik ve Güzellik Merkezi</t>
@@ -11199,10 +12736,6 @@
           <t>+90 505 333 40 93</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr"/>
-      <c r="H150" t="inlineStr"/>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr">
         <is>
           <t>https://hasekiestetik.com/</t>
@@ -11228,7 +12761,6 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
           <t>Diş Hekimi Emre Köse</t>
@@ -11254,11 +12786,6 @@
           <t>+90 212 249 12 76</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr"/>
-      <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr">
         <is>
           <t>4.8</t>
@@ -11279,7 +12806,6 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr">
         <is>
           <t>Estemark</t>
@@ -11310,7 +12836,6 @@
           <t>905366256666</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr">
         <is>
           <t>info@estemark.com</t>
@@ -11346,7 +12871,6 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr">
         <is>
           <t>Vitruvian Clinic - Center of Surgeons</t>
@@ -11377,13 +12901,11 @@
           <t>905353007067</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr">
         <is>
           <t>info@vitruvianclinicpoliklinigi.com</t>
         </is>
       </c>
-      <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr">
         <is>
           <t>https://vitruvianclinicpoliklinigi.com/</t>
@@ -11409,7 +12931,6 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr">
         <is>
           <t>Best Dentist Istanbul | Dental | Hair Transplant | Hospital</t>
@@ -11440,8 +12961,6 @@
           <t>905387641773</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr"/>
-      <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr">
         <is>
           <t>medicalofistanbul</t>
@@ -11472,7 +12991,6 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr">
         <is>
           <t>Avrupa Göz Estetik</t>
@@ -11498,10 +13016,6 @@
           <t>+90 532 704 41 02</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr"/>
-      <c r="H155" t="inlineStr"/>
-      <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr">
         <is>
           <t>http://www.avrupagozestetik.com/</t>
@@ -11527,7 +13041,6 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr">
         <is>
           <t>Anka Estetik ve Plastik Cerrahi, Doç.Dr.Anı Çinpolat-Doç.Dr.Gamze Bektaş</t>
@@ -11558,7 +13071,6 @@
           <t>905304968989</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr">
         <is>
           <t>info@ankaplasticsurgery.com</t>
@@ -11594,7 +13106,6 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr">
         <is>
           <t>Jin. Op. Dr. Karin Bozkurt Kadın Hastalıkları ve Doğum Uzmanı, Tüp Bebek Beyoğlu İstanbul</t>
@@ -11620,10 +13131,6 @@
           <t>+90 532 166 63 20</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr"/>
-      <c r="H157" t="inlineStr"/>
-      <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr">
         <is>
           <t>https://karinbozkurt.com/</t>
@@ -11649,7 +13156,6 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr">
         <is>
           <t>GalataDent Istanbul Diş Kliniği</t>
@@ -11675,13 +13181,11 @@
           <t>+90 542 749 42 82</t>
         </is>
       </c>
-      <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr">
         <is>
           <t>bandarslotsonline@bandarslot.us.com</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr">
         <is>
           <t>slot88resmi</t>
@@ -11712,7 +13216,6 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr">
         <is>
           <t>Taksim Dental Clinic</t>
@@ -11738,11 +13241,6 @@
           <t>+90 543 804 92 06</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr"/>
-      <c r="H159" t="inlineStr"/>
-      <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr">
         <is>
           <t>4.8</t>
@@ -11763,7 +13261,6 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr">
         <is>
           <t>Venüs Poliklinik</t>
@@ -11789,10 +13286,6 @@
           <t>+90 530 960 88 05</t>
         </is>
       </c>
-      <c r="G160" t="inlineStr"/>
-      <c r="H160" t="inlineStr"/>
-      <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr">
         <is>
           <t>https://venushealthpoint.com/</t>
@@ -11818,7 +13311,6 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr">
         <is>
           <t>Health Fly Dental</t>
@@ -11849,7 +13341,6 @@
           <t>447367832577, 905309744887</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr">
         <is>
           <t>info@healthflydental.com</t>
@@ -11885,7 +13376,6 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr">
         <is>
           <t>porteofistanbul-saçekimi</t>
@@ -11916,8 +13406,6 @@
           <t>905524120578</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr"/>
-      <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr">
         <is>
           <t>porteistanbul</t>
@@ -11948,7 +13436,6 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr"/>
       <c r="B163" t="inlineStr">
         <is>
           <t>Renew Beauty Kadıköy | Cilt Bakımı, Lazer Epilasyon, Zayıflama ve Kaş Tasarım</t>
@@ -11979,7 +13466,6 @@
           <t>908505326667</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr">
         <is>
           <t>info@renew.com.tr</t>
@@ -12015,7 +13501,6 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr"/>
       <c r="B164" t="inlineStr">
         <is>
           <t>Clinic surprise experts</t>
@@ -12041,9 +13526,6 @@
           <t>+90 507 507 55 57</t>
         </is>
       </c>
-      <c r="G164" t="inlineStr"/>
-      <c r="H164" t="inlineStr"/>
-      <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr">
         <is>
           <t>_n, rsrc.php</t>
@@ -12074,7 +13556,6 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr">
         <is>
           <t>Babucçu Estetik Merkezi</t>
@@ -12105,7 +13586,6 @@
           <t>905492343443</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr">
         <is>
           <t>info@babuccu.com</t>
@@ -12141,7 +13621,6 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr"/>
       <c r="B166" t="inlineStr">
         <is>
           <t>MOON HAIR</t>
@@ -12167,10 +13646,6 @@
           <t>+90 536 281 34 85</t>
         </is>
       </c>
-      <c r="G166" t="inlineStr"/>
-      <c r="H166" t="inlineStr"/>
-      <c r="I166" t="inlineStr"/>
-      <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr">
         <is>
           <t>http://moonhairoxygen.com/</t>
@@ -12196,7 +13671,6 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr"/>
       <c r="B167" t="inlineStr">
         <is>
           <t>The best dental clinic in turkey | dental implants in turkey | All on 6 | All on 4 | Zirconium crowns | ALL ON X clinic</t>
@@ -12227,7 +13701,6 @@
           <t>905344558555</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr">
         <is>
           <t>info@all-on-x.online</t>
@@ -12263,7 +13736,6 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr">
         <is>
           <t>Cosmostation Cosmetic &amp; Beauty Store Taksim İstiklal</t>
@@ -12299,7 +13771,6 @@
           <t>taksimface@gmail.com</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr">
         <is>
           <t>cosmostation</t>
@@ -12330,7 +13801,6 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr">
         <is>
           <t>Diş Hekimi Meltem Uzun</t>
@@ -12356,11 +13826,6 @@
           <t>+90 212 361 21 41</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr"/>
-      <c r="H169" t="inlineStr"/>
-      <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr">
         <is>
           <t>5</t>
@@ -12381,7 +13846,6 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr"/>
       <c r="B170" t="inlineStr">
         <is>
           <t>Best Dentist in Turkey İstanbul - Dr. Samet - Dental Implants Turkey - Best Dental Clinic in Turkey</t>
@@ -12407,11 +13871,6 @@
           <t>+90 505 618 57 77</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr"/>
-      <c r="H170" t="inlineStr"/>
-      <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr">
         <is>
           <t>5</t>
@@ -12432,7 +13891,6 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr"/>
       <c r="B171" t="inlineStr">
         <is>
           <t>Mass beauty centre</t>
@@ -12458,9 +13916,6 @@
           <t>+90 533 927 44 54</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr"/>
-      <c r="H171" t="inlineStr"/>
-      <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr">
         <is>
           <t>_n, rsrc.php</t>
@@ -12491,7 +13946,6 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr">
         <is>
           <t>Diş Hekimi Rojda Bülbül</t>
@@ -12517,9 +13971,6 @@
           <t>+90 530 234 21 01</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr"/>
-      <c r="H172" t="inlineStr"/>
-      <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr">
         <is>
           <t>_n, rsrc.php</t>
@@ -12550,7 +14001,6 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr"/>
       <c r="B173" t="inlineStr">
         <is>
           <t>ELAY CLINIC…rhinoplasty,breast augmentation,bbl,liposuction,cosmetic surgery</t>
@@ -12621,7 +14071,6 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr"/>
       <c r="B174" t="inlineStr">
         <is>
           <t>Taksim Beauty Center</t>
@@ -12647,11 +14096,6 @@
           <t>+90 507 847 77 22</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr"/>
-      <c r="H174" t="inlineStr"/>
-      <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr">
         <is>
           <t>4.6</t>
@@ -12672,7 +14116,6 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr"/>
       <c r="B175" t="inlineStr">
         <is>
           <t>CITYBEAUTY Kadıköy (CITYSUN) | Cilt Bakımı | Zayıflama | Solaryum | Epilasyon</t>
@@ -12698,11 +14141,6 @@
           <t>+90 216 450 30 32</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr"/>
-      <c r="H175" t="inlineStr"/>
-      <c r="I175" t="inlineStr"/>
-      <c r="J175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr">
         <is>
           <t>4.4</t>
@@ -12723,7 +14161,6 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr"/>
       <c r="B176" t="inlineStr">
         <is>
           <t>Vizyon Ağız ve Diş Sağlığı Polikliniği</t>
@@ -12749,10 +14186,6 @@
           <t>+90 212 238 22 99</t>
         </is>
       </c>
-      <c r="G176" t="inlineStr"/>
-      <c r="H176" t="inlineStr"/>
-      <c r="I176" t="inlineStr"/>
-      <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr">
         <is>
           <t>http://vizyondis.com/</t>
@@ -12778,7 +14211,6 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr"/>
       <c r="B177" t="inlineStr">
         <is>
           <t>EPİTEN</t>
@@ -12804,10 +14236,6 @@
           <t>+90 544 374 83 64</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr"/>
-      <c r="H177" t="inlineStr"/>
-      <c r="I177" t="inlineStr"/>
-      <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr">
         <is>
           <t>https://www.igneliepilasyon.com.tr/</t>
@@ -12833,7 +14261,6 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr"/>
       <c r="B178" t="inlineStr">
         <is>
           <t>Bahariye Pınar Akkoyun Beauty</t>
@@ -12859,10 +14286,6 @@
           <t>+90 542 737 00 00</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr"/>
-      <c r="H178" t="inlineStr"/>
-      <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr">
         <is>
           <t>http://pinarakkoyun.com/</t>
@@ -12888,7 +14311,6 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr"/>
       <c r="B179" t="inlineStr">
         <is>
           <t>Derma Sağlık Estetik Merkezi</t>
@@ -12914,9 +14336,6 @@
           <t>+90 212 531 90 44</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr"/>
-      <c r="H179" t="inlineStr"/>
-      <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr">
         <is>
           <t>_n, rsrc.php</t>
@@ -12947,7 +14366,6 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr"/>
       <c r="B180" t="inlineStr">
         <is>
           <t>Hair Transplant Clinic Turkey</t>
@@ -12973,14 +14391,11 @@
           <t>+90 554 893 64 79</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr"/>
-      <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr">
         <is>
           <t>info@teslatravel.com</t>
         </is>
       </c>
-      <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr">
         <is>
           <t>https://www.teslatravel.com/hair-transplant-clinic-turkey/</t>
@@ -13006,7 +14421,6 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr"/>
       <c r="B181" t="inlineStr">
         <is>
           <t>Estetik</t>
@@ -13027,12 +14441,6 @@
           <t>Güzellik Salonu</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr"/>
-      <c r="G181" t="inlineStr"/>
-      <c r="H181" t="inlineStr"/>
-      <c r="I181" t="inlineStr"/>
-      <c r="J181" t="inlineStr"/>
-      <c r="K181" t="inlineStr"/>
       <c r="L181" t="inlineStr">
         <is>
           <t>4.1</t>
@@ -13053,7 +14461,6 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr"/>
       <c r="B182" t="inlineStr">
         <is>
           <t>Eleven Estetik</t>
@@ -13084,7 +14491,6 @@
           <t>905011032511, 905011552511</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr">
         <is>
           <t>info@elevenestetik.com</t>
@@ -13120,7 +14526,6 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr"/>
       <c r="B183" t="inlineStr">
         <is>
           <t>PERADENTAL</t>
@@ -13146,11 +14551,6 @@
           <t>+90 212 243 66 35</t>
         </is>
       </c>
-      <c r="G183" t="inlineStr"/>
-      <c r="H183" t="inlineStr"/>
-      <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr">
         <is>
           <t>5</t>
@@ -13171,7 +14571,6 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr"/>
       <c r="B184" t="inlineStr">
         <is>
           <t>ELEGANCE BEAUTY CENTRE</t>
@@ -13197,11 +14596,6 @@
           <t>+90 501 086 85 85</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr"/>
-      <c r="H184" t="inlineStr"/>
-      <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
-      <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr">
         <is>
           <t>4.8</t>
@@ -13222,7 +14616,6 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr"/>
       <c r="B185" t="inlineStr">
         <is>
           <t>Dr.. Mahdi Daoud</t>
@@ -13243,12 +14636,6 @@
           <t>Estetik Cerrah</t>
         </is>
       </c>
-      <c r="F185" t="inlineStr"/>
-      <c r="G185" t="inlineStr"/>
-      <c r="H185" t="inlineStr"/>
-      <c r="I185" t="inlineStr"/>
-      <c r="J185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
       <c r="L185" t="inlineStr">
         <is>
           <t>4.9</t>
@@ -13269,7 +14656,6 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr"/>
       <c r="B186" t="inlineStr">
         <is>
           <t>Suave Dental Clinic</t>
@@ -13300,7 +14686,6 @@
           <t>905426992911</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr">
         <is>
           <t>contact@suaveclinic.com, info@suaveclinic.com</t>
@@ -13336,7 +14721,6 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr"/>
       <c r="B187" t="inlineStr">
         <is>
           <t>Dentaroyal Ağız ve Diş Sağlığı Polikliniği</t>
@@ -13407,7 +14791,6 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr"/>
       <c r="B188" t="inlineStr">
         <is>
           <t>Kuzey Estetik Üsküdar</t>
@@ -13428,12 +14811,6 @@
           <t>Güzellik Salonu</t>
         </is>
       </c>
-      <c r="F188" t="inlineStr"/>
-      <c r="G188" t="inlineStr"/>
-      <c r="H188" t="inlineStr"/>
-      <c r="I188" t="inlineStr"/>
-      <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr">
         <is>
           <t>4.9</t>
@@ -13454,7 +14831,6 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" t="inlineStr"/>
       <c r="B189" t="inlineStr">
         <is>
           <t>Hair Center Of Turkey Medical Center | HCT Best Hair Transplant Clinic in Turkey</t>
@@ -13490,7 +14866,6 @@
           <t>sales@haircenterofturkey.com</t>
         </is>
       </c>
-      <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr">
         <is>
           <t>haircenterofturkey</t>
@@ -13521,7 +14896,6 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="inlineStr"/>
       <c r="B190" t="inlineStr">
         <is>
           <t>Clinic Galata | Sculptra, Liquid Facelift &amp; Medical Aesthetic Clinic Istanbul</t>
@@ -13592,7 +14966,6 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="inlineStr"/>
       <c r="B191" t="inlineStr">
         <is>
           <t>Senamoni Güzellik Merkezi</t>
@@ -13613,12 +14986,6 @@
           <t>Güzellik Salonu</t>
         </is>
       </c>
-      <c r="F191" t="inlineStr"/>
-      <c r="G191" t="inlineStr"/>
-      <c r="H191" t="inlineStr"/>
-      <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
-      <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr">
         <is>
           <t>4.6</t>
@@ -13639,7 +15006,6 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="inlineStr"/>
       <c r="B192" t="inlineStr">
         <is>
           <t>Armadent Ortodonti Kliniği</t>
@@ -13665,10 +15031,6 @@
           <t>+90 530 011 89 19</t>
         </is>
       </c>
-      <c r="G192" t="inlineStr"/>
-      <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr"/>
-      <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
         <is>
           <t>http://www.armadent.com.tr/</t>
@@ -13694,7 +15056,6 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" t="inlineStr"/>
       <c r="B193" t="inlineStr">
         <is>
           <t>Özel Mercan Ağız ve Diş Sağlığı Polikliniği</t>
@@ -13720,14 +15081,11 @@
           <t>+90 544 790 31 35</t>
         </is>
       </c>
-      <c r="G193" t="inlineStr"/>
-      <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr">
         <is>
           <t>info@mercandissaglik.com</t>
         </is>
       </c>
-      <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
           <t>https://mercandissaglik.com/</t>
@@ -13753,7 +15111,6 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" t="inlineStr"/>
       <c r="B194" t="inlineStr">
         <is>
           <t>DenTaksim 360</t>
@@ -13779,11 +15136,6 @@
           <t>+90 505 011 11 99</t>
         </is>
       </c>
-      <c r="G194" t="inlineStr"/>
-      <c r="H194" t="inlineStr"/>
-      <c r="I194" t="inlineStr"/>
-      <c r="J194" t="inlineStr"/>
-      <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr">
         <is>
           <t>4.7</t>
@@ -13804,7 +15156,6 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" t="inlineStr"/>
       <c r="B195" t="inlineStr">
         <is>
           <t>First Class Beauty Centre</t>
@@ -13830,11 +15181,6 @@
           <t>+90 544 376 53 47</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr"/>
-      <c r="H195" t="inlineStr"/>
-      <c r="I195" t="inlineStr"/>
-      <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr">
         <is>
           <t>4.7</t>
@@ -13855,7 +15201,6 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr"/>
       <c r="B196" t="inlineStr">
         <is>
           <t>Nurhan Arya Güzellik Salonu</t>
@@ -13881,11 +15226,6 @@
           <t>+90 541 253 69 43</t>
         </is>
       </c>
-      <c r="G196" t="inlineStr"/>
-      <c r="H196" t="inlineStr"/>
-      <c r="I196" t="inlineStr"/>
-      <c r="J196" t="inlineStr"/>
-      <c r="K196" t="inlineStr"/>
       <c r="L196" t="inlineStr">
         <is>
           <t>5</t>
@@ -13906,7 +15246,6 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" t="inlineStr"/>
       <c r="B197" t="inlineStr">
         <is>
           <t>Universal Hair Transplant - Best Hair Transplant in Turkey</t>
@@ -13937,7 +15276,6 @@
           <t>905446573616</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
           <t>contact@dentalstud.io, info@eurekatravelturkey.com, info@universalhairtransplant.com</t>
@@ -13973,7 +15311,6 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" t="inlineStr"/>
       <c r="B198" t="inlineStr">
         <is>
           <t>حياة دنت كلينيك - Hayatdent Clinic</t>
@@ -14009,7 +15346,6 @@
           <t>hayatdentclinic@outlook.com</t>
         </is>
       </c>
-      <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr">
         <is>
           <t>clinichayatdent, hayatdentclinic</t>
@@ -14040,7 +15376,6 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" t="inlineStr"/>
       <c r="B199" t="inlineStr">
         <is>
           <t>Diş Hekimi Fatma İnci</t>
@@ -14066,11 +15401,6 @@
           <t>+90 212 293 91 24</t>
         </is>
       </c>
-      <c r="G199" t="inlineStr"/>
-      <c r="H199" t="inlineStr"/>
-      <c r="I199" t="inlineStr"/>
-      <c r="J199" t="inlineStr"/>
-      <c r="K199" t="inlineStr"/>
       <c r="L199" t="inlineStr">
         <is>
           <t>4.8</t>
@@ -14091,7 +15421,6 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" t="inlineStr"/>
       <c r="B200" t="inlineStr">
         <is>
           <t>Balçova Özel Novar 3 Polikliniği | Lazer Epilasyon | Dudak Dolgu | Dövme Silme</t>
@@ -14117,7 +15446,6 @@
           <t>+90 232 404 44 00</t>
         </is>
       </c>
-      <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr">
         <is>
           <t>yusuf@novarpoliklinik.com</t>
@@ -14158,7 +15486,6 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" t="inlineStr"/>
       <c r="B201" t="inlineStr">
         <is>
           <t>Özel Avrupadent Bozyaka Ağız ve Diş Sağlığı Polikliniği</t>
@@ -14189,7 +15516,6 @@
           <t>905538326035</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr"/>
       <c r="I201" t="inlineStr">
         <is>
           <t>info@avrupadent.com.tr</t>
@@ -14225,7 +15551,6 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" t="inlineStr"/>
       <c r="B202" t="inlineStr">
         <is>
           <t>Linemed Poliklinik İzmir</t>
@@ -14256,7 +15581,6 @@
           <t>905394112647</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr"/>
       <c r="I202" t="inlineStr">
         <is>
           <t>info@linemed.com.tr</t>
@@ -14292,7 +15616,6 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="inlineStr"/>
       <c r="B203" t="inlineStr">
         <is>
           <t>Clinichair</t>
@@ -14323,7 +15646,6 @@
           <t>905304638315, 905465422092</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr"/>
       <c r="I203" t="inlineStr">
         <is>
           <t>info@clinichair.com</t>
@@ -14359,7 +15681,6 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" t="inlineStr"/>
       <c r="B204" t="inlineStr">
         <is>
           <t>Likya Saç Ekim &amp; Estetik | Bayraklı</t>
@@ -14430,7 +15751,6 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" t="inlineStr"/>
       <c r="B205" t="inlineStr">
         <is>
           <t>Hair Information Clinic - Saç Ekimi</t>
@@ -14461,7 +15781,6 @@
           <t>905302814247</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr"/>
       <c r="I205" t="inlineStr">
         <is>
           <t>info@hairinfoclinic.com</t>
@@ -14497,7 +15816,6 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" t="inlineStr"/>
       <c r="B206" t="inlineStr">
         <is>
           <t>İzmir Klinik</t>
@@ -14523,11 +15841,6 @@
           <t>+90 539 654 47 26</t>
         </is>
       </c>
-      <c r="G206" t="inlineStr"/>
-      <c r="H206" t="inlineStr"/>
-      <c r="I206" t="inlineStr"/>
-      <c r="J206" t="inlineStr"/>
-      <c r="K206" t="inlineStr"/>
       <c r="L206" t="inlineStr">
         <is>
           <t>4.7</t>
@@ -14548,7 +15861,6 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" t="inlineStr"/>
       <c r="B207" t="inlineStr">
         <is>
           <t>Op. Dr. Mustafa Öksüz İzmir Estetik ve Plastik Cerrahi Meme Estetiği Botox Filler Burun Estetiği Dudak Dolgusu</t>
@@ -14619,7 +15931,6 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" t="inlineStr"/>
       <c r="B208" t="inlineStr">
         <is>
           <t>Özel Avrupadent Karabağlar Ağız ve Diş Sağlığı Polikliniği</t>
@@ -14650,7 +15961,6 @@
           <t>905538326035</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr"/>
       <c r="I208" t="inlineStr">
         <is>
           <t>info@avrupadent.com.tr</t>
@@ -14686,7 +15996,6 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" t="inlineStr"/>
       <c r="B209" t="inlineStr">
         <is>
           <t>Yeşilyurt Dental - Bozyaka Şubesi | Diş doktoru bozyaka, İmplant İzmir, Zirkonyum İzmir</t>
@@ -14712,8 +16021,6 @@
           <t>+90 552 665 40 24</t>
         </is>
       </c>
-      <c r="G209" t="inlineStr"/>
-      <c r="H209" t="inlineStr"/>
       <c r="I209" t="inlineStr">
         <is>
           <t>info@dentco.net, info@yesilyurtdent.com.tr</t>
@@ -14749,7 +16056,6 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" t="inlineStr"/>
       <c r="B210" t="inlineStr">
         <is>
           <t>İzmir Estetik Cerrahi Kliniği Dr. Tolgahan Alpaydın | Meme Büyütme | Burun Estetiği | Liposuction |</t>
@@ -14820,7 +16126,6 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" t="inlineStr"/>
       <c r="B211" t="inlineStr">
         <is>
           <t>Özel Dr. Ulusan Polikliniği | Saç Ekimi İzmir</t>
@@ -14841,9 +16146,6 @@
           <t>Saç Transplantasyonu Kliniği</t>
         </is>
       </c>
-      <c r="F211" t="inlineStr"/>
-      <c r="G211" t="inlineStr"/>
-      <c r="H211" t="inlineStr"/>
       <c r="I211" t="inlineStr">
         <is>
           <t>info@ulusanclinic.com</t>
@@ -14879,7 +16181,6 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" t="inlineStr"/>
       <c r="B212" t="inlineStr">
         <is>
           <t>Elif Dinçarslan Polikliniği - İzmir Saç Ekimi &amp; Estetik Merkezi</t>
@@ -14910,7 +16211,6 @@
           <t>905444216611</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr"/>
       <c r="I212" t="inlineStr">
         <is>
           <t>info@elifdincarslanpoliklinigi.com</t>
@@ -14946,7 +16246,6 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" t="inlineStr"/>
       <c r="B213" t="inlineStr">
         <is>
           <t>Zesu Estetik</t>
@@ -14972,14 +16271,11 @@
           <t>+90 555 516 80 80</t>
         </is>
       </c>
-      <c r="G213" t="inlineStr"/>
       <c r="H213" t="inlineStr">
         <is>
           <t>webmaster@zesuestetik.com</t>
         </is>
       </c>
-      <c r="I213" t="inlineStr"/>
-      <c r="J213" t="inlineStr"/>
       <c r="K213" t="inlineStr">
         <is>
           <t>https://zesuestetik.com/</t>
@@ -15005,7 +16301,6 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" t="inlineStr"/>
       <c r="B214" t="inlineStr">
         <is>
           <t>Op. Dr. Türker Üstün Estetik Plastik Cerrahi Kliniği | Jinekomasti İzmir</t>
@@ -15031,10 +16326,6 @@
           <t>+90 532 425 26 16</t>
         </is>
       </c>
-      <c r="G214" t="inlineStr"/>
-      <c r="H214" t="inlineStr"/>
-      <c r="I214" t="inlineStr"/>
-      <c r="J214" t="inlineStr"/>
       <c r="K214" t="inlineStr">
         <is>
           <t>http://www.turkerustun.com/</t>
@@ -15060,7 +16351,6 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" t="inlineStr"/>
       <c r="B215" t="inlineStr">
         <is>
           <t>İzmir saç ekim merkezi maxhairclinic / maxhairizmir/saç ekim İzmir</t>
@@ -15086,10 +16376,6 @@
           <t>+90 537 628 09 56</t>
         </is>
       </c>
-      <c r="G215" t="inlineStr"/>
-      <c r="H215" t="inlineStr"/>
-      <c r="I215" t="inlineStr"/>
-      <c r="J215" t="inlineStr"/>
       <c r="K215" t="inlineStr">
         <is>
           <t>https://maxhairtransplant.com/</t>
@@ -15115,7 +16401,6 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" t="inlineStr"/>
       <c r="B216" t="inlineStr">
         <is>
           <t>DentaPoint International - Alsancak Şubesi Zirkonyum , Diş İmplantı , Estetik Diş Tedavileri , Çocuk Diş</t>
@@ -15151,7 +16436,6 @@
           <t>dentapointalsancak@gmail.com, dentapointdis@hotmail.com, dentapointdisbostanli@gmail.com</t>
         </is>
       </c>
-      <c r="I216" t="inlineStr"/>
       <c r="J216" t="inlineStr">
         <is>
           <t>dentapoint</t>
@@ -15182,7 +16466,6 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" t="inlineStr"/>
       <c r="B217" t="inlineStr">
         <is>
           <t>Özel Çağdaş Dent Ağız ve Diş Sağlığı Polikliniği</t>
@@ -15208,8 +16491,6 @@
           <t>+90 530 355 15 75</t>
         </is>
       </c>
-      <c r="G217" t="inlineStr"/>
-      <c r="H217" t="inlineStr"/>
       <c r="I217" t="inlineStr">
         <is>
           <t>info@cagdasdent.com.tr</t>
@@ -15245,7 +16526,6 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" t="inlineStr"/>
       <c r="B218" t="inlineStr">
         <is>
           <t>Özel Heraderma Polikliniği</t>
@@ -15276,7 +16556,6 @@
           <t>905302902701</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr"/>
       <c r="I218" t="inlineStr">
         <is>
           <t>info@heraderma.com</t>
@@ -15312,7 +16591,6 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" t="inlineStr"/>
       <c r="B219" t="inlineStr">
         <is>
           <t>Özel Eski İzmir Ağız Ve Dış Sağlığı Polikliniği</t>
@@ -15338,10 +16616,6 @@
           <t>+90 530 161 33 89</t>
         </is>
       </c>
-      <c r="G219" t="inlineStr"/>
-      <c r="H219" t="inlineStr"/>
-      <c r="I219" t="inlineStr"/>
-      <c r="J219" t="inlineStr"/>
       <c r="K219" t="inlineStr">
         <is>
           <t>https://eskiizmirdispoliklinigi.com/</t>
@@ -15367,7 +16641,6 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" t="inlineStr"/>
       <c r="B220" t="inlineStr">
         <is>
           <t>Üçkuyular Ağız ve Diş Sağlığı Polikliniği</t>
@@ -15393,10 +16666,6 @@
           <t>+90 232 277 62 42</t>
         </is>
       </c>
-      <c r="G220" t="inlineStr"/>
-      <c r="H220" t="inlineStr"/>
-      <c r="I220" t="inlineStr"/>
-      <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr">
         <is>
           <t>http://www.uckuyulardis.com.tr/</t>
@@ -15422,7 +16691,6 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" t="inlineStr"/>
       <c r="B221" t="inlineStr">
         <is>
           <t>İzmir Saç Ekim Merkezi - Art Hair Clinic</t>
@@ -15448,8 +16716,6 @@
           <t>+90 537 549 50 35</t>
         </is>
       </c>
-      <c r="G221" t="inlineStr"/>
-      <c r="H221" t="inlineStr"/>
       <c r="I221" t="inlineStr">
         <is>
           <t>info@arthairclinic.net</t>
@@ -15485,7 +16751,6 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" t="inlineStr"/>
       <c r="B222" t="inlineStr">
         <is>
           <t>Özel Atlas Dental Ağız ve Diş Sağlığı Polikliniği</t>
@@ -15516,7 +16781,6 @@
           <t>905528308554</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr"/>
       <c r="I222" t="inlineStr">
         <is>
           <t>info@atlasdental.com.tr</t>
@@ -15552,7 +16816,6 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" t="inlineStr"/>
       <c r="B223" t="inlineStr">
         <is>
           <t>Opr. Dr. Ebru Durmuş - Estetik ve Plastik cerrahi</t>
@@ -15578,9 +16841,6 @@
           <t>+90 553 026 75 47</t>
         </is>
       </c>
-      <c r="G223" t="inlineStr"/>
-      <c r="H223" t="inlineStr"/>
-      <c r="I223" t="inlineStr"/>
       <c r="J223" t="inlineStr">
         <is>
           <t>drebruulgerdurmus</t>
@@ -15611,7 +16871,6 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" t="inlineStr"/>
       <c r="B224" t="inlineStr">
         <is>
           <t>Op. Dr. Özgür Sunay</t>
@@ -15637,10 +16896,6 @@
           <t>+90 232 290 57 57</t>
         </is>
       </c>
-      <c r="G224" t="inlineStr"/>
-      <c r="H224" t="inlineStr"/>
-      <c r="I224" t="inlineStr"/>
-      <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr">
         <is>
           <t>http://www.ozgursunay.com/</t>
@@ -15666,7 +16921,6 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" t="inlineStr"/>
       <c r="B225" t="inlineStr">
         <is>
           <t>Erna Hair Clinic İzmir Saç Ekim Merkezi</t>
@@ -15692,10 +16946,6 @@
           <t>+90 545 100 12 37</t>
         </is>
       </c>
-      <c r="G225" t="inlineStr"/>
-      <c r="H225" t="inlineStr"/>
-      <c r="I225" t="inlineStr"/>
-      <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr">
         <is>
           <t>https://www.ernahairclinic.com/</t>
@@ -15721,7 +16971,6 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" t="inlineStr"/>
       <c r="B226" t="inlineStr">
         <is>
           <t>Prp Saç Tedavisi İzmir | Ossi Hair | İzmir Saç Ekimi | Mezoterapi İzmir | PRP İzmir</t>
@@ -15752,7 +17001,6 @@
           <t>905523330673</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr"/>
       <c r="I226" t="inlineStr">
         <is>
           <t>info@ossihair.com</t>
@@ -15788,7 +17036,6 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" t="inlineStr"/>
       <c r="B227" t="inlineStr">
         <is>
           <t>İzmir Saç Ekim Merkezi | Loya Clinic | Fue saç ekimi | İzmir saç PRP ve Mezoterapi | Sakal ekimi | Kaş ekimi</t>
@@ -15819,7 +17066,6 @@
           <t>905307475692</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr"/>
       <c r="I227" t="inlineStr">
         <is>
           <t>info@loyaclinic.com</t>
@@ -15855,7 +17101,6 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" t="inlineStr"/>
       <c r="B228" t="inlineStr">
         <is>
           <t>Newhair İzmir, Protez saç, Saç Protezi, Saç Ekimi, Kemoterapi, Hair Replacement, Toupee</t>
@@ -15886,7 +17131,6 @@
           <t>905549879066</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr"/>
       <c r="I228" t="inlineStr">
         <is>
           <t>info@newhair.com.tr</t>
@@ -15922,7 +17166,6 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" t="inlineStr"/>
       <c r="B229" t="inlineStr">
         <is>
           <t>DENT BALÇOVA - Balçova Ağız ve Diş Sağlığı Polikliniği</t>
@@ -15948,13 +17191,11 @@
           <t>+90 545 113 35 35</t>
         </is>
       </c>
-      <c r="G229" t="inlineStr"/>
       <c r="H229" t="inlineStr">
         <is>
           <t>dentbalcova@gmail.com</t>
         </is>
       </c>
-      <c r="I229" t="inlineStr"/>
       <c r="J229" t="inlineStr">
         <is>
           <t>wix</t>
@@ -15985,7 +17226,6 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" t="inlineStr"/>
       <c r="B230" t="inlineStr">
         <is>
           <t>CEON Ağız ve Diş Sağlığı Polikliniği</t>
@@ -16021,7 +17261,6 @@
           <t>narlidere@ceondent.com, u003enarlidere@ceondent.com</t>
         </is>
       </c>
-      <c r="I230" t="inlineStr"/>
       <c r="J230" t="inlineStr">
         <is>
           <t>ceondent</t>
@@ -16052,7 +17291,6 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" t="inlineStr"/>
       <c r="B231" t="inlineStr">
         <is>
           <t>İzmir Dent Özel Ağız ve Diş Sağlığı Polikliniği</t>
@@ -16083,7 +17321,6 @@
           <t>905539543530</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr"/>
       <c r="I231" t="inlineStr">
         <is>
           <t>info@izmirdent.com.tr</t>
@@ -16119,7 +17356,6 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" t="inlineStr"/>
       <c r="B232" t="inlineStr">
         <is>
           <t>Arya Clinic Estetik ve Güzellik Merkezi</t>
@@ -16145,11 +17381,6 @@
           <t>+90 232 426 55 62</t>
         </is>
       </c>
-      <c r="G232" t="inlineStr"/>
-      <c r="H232" t="inlineStr"/>
-      <c r="I232" t="inlineStr"/>
-      <c r="J232" t="inlineStr"/>
-      <c r="K232" t="inlineStr"/>
       <c r="L232" t="inlineStr">
         <is>
           <t>4.4</t>
@@ -16170,7 +17401,6 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" t="inlineStr"/>
       <c r="B233" t="inlineStr">
         <is>
           <t>İzmir Saç Ekim Merkezi | Kuzey Hair Clinic</t>
@@ -16241,7 +17471,6 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" t="inlineStr"/>
       <c r="B234" t="inlineStr">
         <is>
           <t>Likya Saç Ekim &amp; Estetik | Alsancak</t>
@@ -16267,10 +17496,6 @@
           <t>+90 232 465 12 55</t>
         </is>
       </c>
-      <c r="G234" t="inlineStr"/>
-      <c r="H234" t="inlineStr"/>
-      <c r="I234" t="inlineStr"/>
-      <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr">
         <is>
           <t>http://www.likyaestetik.com/</t>
@@ -16296,7 +17521,6 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" t="inlineStr"/>
       <c r="B235" t="inlineStr">
         <is>
           <t>Maya Beauty Bay ve Bayan Güzellik Salonu</t>
@@ -16322,11 +17546,6 @@
           <t>+90 543 911 43 88</t>
         </is>
       </c>
-      <c r="G235" t="inlineStr"/>
-      <c r="H235" t="inlineStr"/>
-      <c r="I235" t="inlineStr"/>
-      <c r="J235" t="inlineStr"/>
-      <c r="K235" t="inlineStr"/>
       <c r="L235" t="inlineStr">
         <is>
           <t>4.8</t>
@@ -16347,7 +17566,6 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" t="inlineStr"/>
       <c r="B236" t="inlineStr">
         <is>
           <t>Avrupa Estetik ve Güzellik Merkezi | Soprano Ice Buz Lazer İzmir-Cilt Bakımı-Lazer Epilasyon İzmir-Beauty Center İzmir</t>
@@ -16373,14 +17591,11 @@
           <t>+90 553 302 09 00</t>
         </is>
       </c>
-      <c r="G236" t="inlineStr"/>
-      <c r="H236" t="inlineStr"/>
       <c r="I236" t="inlineStr">
         <is>
           <t>info@avrupaestetikguzellik.com</t>
         </is>
       </c>
-      <c r="J236" t="inlineStr"/>
       <c r="K236" t="inlineStr">
         <is>
           <t>https://avrupaestetikguzellik.com/</t>
@@ -16406,7 +17621,6 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" t="inlineStr"/>
       <c r="B237" t="inlineStr">
         <is>
           <t>Balçova Diş Hekimi | Diş Hekimi M. Halil Yücesoy Diş Polikinliği</t>
@@ -16437,13 +17651,11 @@
           <t>905359867201</t>
         </is>
       </c>
-      <c r="H237" t="inlineStr"/>
       <c r="I237" t="inlineStr">
         <is>
           <t>info@dishekimihalilyucesoy.com.tr</t>
         </is>
       </c>
-      <c r="J237" t="inlineStr"/>
       <c r="K237" t="inlineStr">
         <is>
           <t>https://dishekimihalilyucesoy.com.tr/</t>
@@ -16469,7 +17681,6 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" t="inlineStr"/>
       <c r="B238" t="inlineStr">
         <is>
           <t>Balçova Beyza SAMANCI PEKTÜRK Diş Kliniği</t>
@@ -16495,11 +17706,6 @@
           <t>+90 232 278 90 90</t>
         </is>
       </c>
-      <c r="G238" t="inlineStr"/>
-      <c r="H238" t="inlineStr"/>
-      <c r="I238" t="inlineStr"/>
-      <c r="J238" t="inlineStr"/>
-      <c r="K238" t="inlineStr"/>
       <c r="L238" t="inlineStr">
         <is>
           <t>5</t>
@@ -16520,7 +17726,6 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" t="inlineStr"/>
       <c r="B239" t="inlineStr">
         <is>
           <t>Dt. Ezgi Aydın Diş Muayenehanesi</t>
@@ -16551,7 +17756,6 @@
           <t>905528573333</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr"/>
       <c r="I239" t="inlineStr">
         <is>
           <t>info@dtezgiaydin.com.tr, info@ezgiaydin.org</t>
@@ -16587,7 +17791,6 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" t="inlineStr"/>
       <c r="B240" t="inlineStr">
         <is>
           <t>Valodent Ağız ve Diş Sağlığı Polikliniği</t>
@@ -16623,7 +17826,6 @@
           <t>valodentgaziemir@gmail.com</t>
         </is>
       </c>
-      <c r="I240" t="inlineStr"/>
       <c r="J240" t="inlineStr">
         <is>
           <t>valodentgaziemir</t>
@@ -16654,7 +17856,6 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" t="inlineStr"/>
       <c r="B241" t="inlineStr">
         <is>
           <t>Sun Diş Polikliniği</t>
@@ -16725,7 +17926,6 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" t="inlineStr"/>
       <c r="B242" t="inlineStr">
         <is>
           <t>Revitalizeinturkey</t>
@@ -16756,7 +17956,6 @@
           <t>447884361546, 905050157330</t>
         </is>
       </c>
-      <c r="H242" t="inlineStr"/>
       <c r="I242" t="inlineStr">
         <is>
           <t>info@revitalizeinturkey.com</t>
@@ -16792,7 +17991,6 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" t="inlineStr"/>
       <c r="B243" t="inlineStr">
         <is>
           <t>Dental Estetik Ağız ve Diş Sağlığı Polikliniği</t>
@@ -16823,8 +18021,6 @@
           <t>905078067805</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr"/>
-      <c r="I243" t="inlineStr"/>
       <c r="J243" t="inlineStr">
         <is>
           <t>dentalaestetic</t>
@@ -16855,7 +18051,6 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" t="inlineStr"/>
       <c r="B244" t="inlineStr">
         <is>
           <t>İzmir Saç Ekimi | İzmir Hair Transplantation | Serena Polikliniği | İzmir Kaş Ekimi</t>
@@ -16886,7 +18081,6 @@
           <t>905323683530</t>
         </is>
       </c>
-      <c r="H244" t="inlineStr"/>
       <c r="I244" t="inlineStr">
         <is>
           <t>info@izmirsacektirme.com</t>
@@ -16922,7 +18116,6 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" t="inlineStr"/>
       <c r="B245" t="inlineStr">
         <is>
           <t>Eges Hair Clinic | İzmir Saç Ekim Merkezi</t>
@@ -16953,7 +18146,6 @@
           <t>905421803050</t>
         </is>
       </c>
-      <c r="H245" t="inlineStr"/>
       <c r="I245" t="inlineStr">
         <is>
           <t>info@egeshairclinic.com</t>
@@ -16989,7 +18181,6 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" t="inlineStr"/>
       <c r="B246" t="inlineStr">
         <is>
           <t>Özel Dental Town Diş Polikliniği Şirinyer Şube</t>
@@ -17015,11 +18206,6 @@
           <t>+90 552 504 05 74</t>
         </is>
       </c>
-      <c r="G246" t="inlineStr"/>
-      <c r="H246" t="inlineStr"/>
-      <c r="I246" t="inlineStr"/>
-      <c r="J246" t="inlineStr"/>
-      <c r="K246" t="inlineStr"/>
       <c r="L246" t="inlineStr">
         <is>
           <t>4.8</t>
@@ -17040,7 +18226,6 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" t="inlineStr"/>
       <c r="B247" t="inlineStr">
         <is>
           <t>İzmir, Konak Deva Ağız ve Diş Sağlığı Polikliniği - Diş Hekimi, İmplant Diş, Kozmetik Diş, Ortodontist</t>
@@ -17071,7 +18256,6 @@
           <t>905456778887</t>
         </is>
       </c>
-      <c r="H247" t="inlineStr"/>
       <c r="I247" t="inlineStr">
         <is>
           <t>info@dentalclinicdeva.com</t>
@@ -17107,7 +18291,6 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" t="inlineStr"/>
       <c r="B248" t="inlineStr">
         <is>
           <t>İzmir Saç Ekimi Merkezi - Hisstohair | Fue saç ekimi | PRP ve Mezoterapi | Sakal ekimi | Kaş ekimi</t>
@@ -17138,8 +18321,6 @@
           <t>05449679127, 905356346002</t>
         </is>
       </c>
-      <c r="H248" t="inlineStr"/>
-      <c r="I248" t="inlineStr"/>
       <c r="J248" t="inlineStr">
         <is>
           <t>izmirsacekimimerkezi</t>
@@ -17170,7 +18351,6 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" t="inlineStr"/>
       <c r="B249" t="inlineStr">
         <is>
           <t>Dent Universe Ağız Ve Diş Sağlığı Polikliniği</t>
@@ -17196,11 +18376,6 @@
           <t>+90 501 093 35 10</t>
         </is>
       </c>
-      <c r="G249" t="inlineStr"/>
-      <c r="H249" t="inlineStr"/>
-      <c r="I249" t="inlineStr"/>
-      <c r="J249" t="inlineStr"/>
-      <c r="K249" t="inlineStr"/>
       <c r="L249" t="inlineStr">
         <is>
           <t>4.9</t>
@@ -17221,7 +18396,6 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" t="inlineStr"/>
       <c r="B250" t="inlineStr">
         <is>
           <t>Dr. Hale Hepçimen | Sıvı Yüz Germe | Botox | Gençlik Aşısı | Dolgu | Medikal Estetik ve Klinik Uygulamalar</t>
@@ -17252,8 +18426,6 @@
           <t>905334637362</t>
         </is>
       </c>
-      <c r="H250" t="inlineStr"/>
-      <c r="I250" t="inlineStr"/>
       <c r="J250" t="inlineStr">
         <is>
           <t>drhalehepcimen</t>
@@ -17284,7 +18456,6 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" t="inlineStr"/>
       <c r="B251" t="inlineStr">
         <is>
           <t>Hair Nirvana | İzmir Saç Ekim Merkezi</t>
@@ -17315,7 +18486,6 @@
           <t>905327338935</t>
         </is>
       </c>
-      <c r="H251" t="inlineStr"/>
       <c r="I251" t="inlineStr">
         <is>
           <t>info@nirvanasac.com</t>
@@ -17351,7 +18521,6 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" t="inlineStr"/>
       <c r="B252" t="inlineStr">
         <is>
           <t>Estetia Estetik Plastik Cerrahi</t>
@@ -17387,7 +18556,6 @@
           <t>atabey58@gmail.com</t>
         </is>
       </c>
-      <c r="I252" t="inlineStr"/>
       <c r="J252" t="inlineStr">
         <is>
           <t>atayatabey, estetiaestetik</t>
@@ -17418,7 +18586,6 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" t="inlineStr"/>
       <c r="B253" t="inlineStr">
         <is>
           <t>Dr.Bekir Hucuptan - Medikal Estetik Uygulamalar - Ozon terapi - Mezoterapi</t>
@@ -17444,14 +18611,11 @@
           <t>+90 544 323 13 20</t>
         </is>
       </c>
-      <c r="G253" t="inlineStr"/>
-      <c r="H253" t="inlineStr"/>
       <c r="I253" t="inlineStr">
         <is>
           <t>bilgi@drbekirhucuptan.com</t>
         </is>
       </c>
-      <c r="J253" t="inlineStr"/>
       <c r="K253" t="inlineStr">
         <is>
           <t>http://www.drbekir.com/</t>
@@ -17477,7 +18641,6 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" t="inlineStr"/>
       <c r="B254" t="inlineStr">
         <is>
           <t>İzmir Saç Ekimi Merkezi | Focus Hair Clinic</t>
@@ -17503,11 +18666,6 @@
           <t>+90 552 001 59 25</t>
         </is>
       </c>
-      <c r="G254" t="inlineStr"/>
-      <c r="H254" t="inlineStr"/>
-      <c r="I254" t="inlineStr"/>
-      <c r="J254" t="inlineStr"/>
-      <c r="K254" t="inlineStr"/>
       <c r="L254" t="inlineStr">
         <is>
           <t>4.8</t>
@@ -17528,7 +18686,6 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" t="inlineStr"/>
       <c r="B255" t="inlineStr">
         <is>
           <t>Mirina Clinic Güzellik &amp; Estetik</t>
@@ -17554,8 +18711,6 @@
           <t>+90 232 245 36 36</t>
         </is>
       </c>
-      <c r="G255" t="inlineStr"/>
-      <c r="H255" t="inlineStr"/>
       <c r="I255" t="inlineStr">
         <is>
           <t>info@mirinaclinic.com</t>
@@ -17591,7 +18746,6 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" t="inlineStr"/>
       <c r="B256" t="inlineStr">
         <is>
           <t>Dt. Oya Vezirköprü Şiren &amp; Dr. Dt. Ecem Güven Diş Kliniği</t>
@@ -17627,7 +18781,6 @@
           <t>dishekimievo@gmail.com, ornek@mail.com</t>
         </is>
       </c>
-      <c r="I256" t="inlineStr"/>
       <c r="J256" t="inlineStr">
         <is>
           <t>ecemveoya</t>
@@ -17663,13 +18816,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -17748,6 +18901,18 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Karar Vericiler</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>LinkedIn'de (Google üzerinden, giriş yapmadan) 241 klinik arandı; 33 kişi elle doğrulandı (yanlış eşleşmeler ve eski çalışanlar çıkarıldı). E-posta: 'bulunan' adresler Apify e-posta aramasından gelir ama alan adları catch-all olduğu için 'riskli'dir; 'tahmini' adresler bulunan örneklerdeki ad.soyad@klinik kalıbıyla üretildi ve DOĞRULANMAMIŞTIR — Instantly'ye koymadan önce doğrulayıcıdan geçir, bounce oranını düşük tut.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads/voice-agent-leads-2026-09.xlsx
+++ b/leads/voice-agent-leads-2026-09.xlsx
@@ -9,13 +9,14 @@
   <sheets>
     <sheet name="Sıcak Lead (doğrulanmış)" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Karar Vericiler (LinkedIn)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Tüm Liste (255)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Nasıl kullanılır" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Sektör Analizi" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Tüm Liste (255)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Nasıl kullanılır" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sıcak Lead (doğrulanmış)'!$A$1:$S$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Karar Vericiler (LinkedIn)'!$A$1:$O$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tüm Liste (255)'!$A$1:$O$256</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Tüm Liste (255)'!$A$1:$O$256</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -24,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,6 +39,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="5">
@@ -75,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -89,6 +94,18 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4078,6 +4095,845 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Sektör (İstanbul)</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>taranan işletme</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>'ulaşamadım' sinyali olan</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>oran</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>toplam yorum</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>yorum</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Oto servis / bayi</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>%17</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>2680</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>En güçlü sinyal: bayilerde çağrı yükü yüksek, randevu ve parça fiyatı telefonla soruluyor.</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Sürücü kursu</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>%17</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>4806</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Kayıt dönemlerinde yoğun arama; kaçan çağrı = kaçan kayıt.</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Araç kiralama</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>%8</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>2224</v>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>7/24 acil ve rezervasyon aramaları; çok dilli (turist) ihtiyaç.</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Butik otel</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>%8</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>13313</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Rezervasyon ve yabancı misafir aramaları; çok dilli ihtiyaç.</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Emlak ofisi</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>%8</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>1223</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>İlan başına çok sayıda arama, danışman sahada olduğu için açılamıyor.</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Restoran (rezervasyon)</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>%0</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>64483</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Çok yorum var ama şikâyetler yemek/servis üzerine; telefon sinyali çıkmadı.</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Veteriner</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>%0</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>2593</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Sinyal çıkmadı; yine de mesai dışı acil arama potansiyeli var.</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+      <c r="I8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Fizik tedavi</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>%0</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>788</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Sinyal çıkmadı; randevu tabanlı, küçük örneklem.</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+      <c r="I9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Nakliyat</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>%0</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>563</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Sinyal çıkmadı; teklif talebi telefonla geliyor, küçük örneklem.</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+      <c r="I10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Pilates stüdyosu</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>%0</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>532</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Sinyal çıkmadı; mesajla (Inboxly) daha uygun.</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Kuaför</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>%0</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Sinyal çıkmadı; randevular çoğunlukla WhatsApp/Instagram → Inboxly.</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+      <c r="I12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Avukatlık bürosu</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>%0</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>143</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Yorum çok az, ölçülemedi.</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+      <c r="I13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Karşılaştırma: Klinikler (önceki tarama)</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>%7</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Daha geniş tarama (26 kelime) ile ~%7 işletmede doğrulanmış sinyal.</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+      <c r="I14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n"/>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Yeni sektörlerden sıcak lead'ler</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+      <c r="I16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>sektör</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>işletme</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>öncelik</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>telefon</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>puan</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>yorum sayısı</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>kanıt (yorum özeti)</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>maps linki</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>oto servis</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Toyota Plaza Kar</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>+90 212 567 22 22</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.toyotakar.com.tr/</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>1046</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>2023–2026 arası 6 şikâyet: telefonlara bakılmıyor, 25 dk bekletip cevap yok, randevu alınamıyor, 'kaç gündür telefonlar açılmıyor' (Mar 2026). Yetkili bayi → bütçe var.</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=Toyota%20Plaza%20Kar&amp;query_place_id=ChIJg-BM1o67yhQRA9D27m2_MUc</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>oto servis</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>otoedirnekapı</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>+90 212 531 30 06</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>http://otoedirnekapi.com.tr/</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>520</v>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Parça fiyatı sormak için arayanlara telefon açılmıyor, WhatsApp'a dönülmüyor (2018, 2021, 2022).</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=otoedirnekap%C4%B1&amp;query_place_id=ChIJTUBpMxG6yhQRJS3aTRFopPI</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>sürücü kursu</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>İstanbul Marmara Sürücü Kursu</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>+90 212 631 59 99</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>http://www.marmaraehliyet.com/</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>357</v>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Kayıt olmak isteyen aday aramış, kimse açmamış — doğrudan kayıp müşteri.</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=%C4%B0stanbul%20Marmara%20S%C3%BCr%C3%BCc%C3%BC%20Kursu&amp;query_place_id=ChIJweJZaSK6yhQR_rbOFjtuwyw</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>sürücü kursu</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Özel Kadıköy Ekip Sürücü Kursu</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>+90 216 346 11 16</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>http://www.ekipsurucukursu.com/</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>489</v>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Kayıt sonrası 'bilgilendireceğiz' denmiş, geri dönüş yapılmamış.</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=%C3%96zel%20Kad%C4%B1k%C3%B6y%20Ekip%20S%C3%BCr%C3%BCc%C3%BC%20Kursu&amp;query_place_id=ChIJx3ufBWa4yhQRI7NMWXMVTrw</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>araç kiralama</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Garenta İstanbul Haliç Araç Kiralama</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>+90 212 945 94 21</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>https://www.garenta.com/tr</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>1320</v>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Acil durumda ulaşılamıyor, defalarca aransa da dönüş yok (Nis 2025). Ulusal marka şubesi.</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=Garenta%20%C4%B0stanbul%20Hali%C3%A7%20Ara%C3%A7%20Kiralama&amp;query_place_id=ChIJQxwa5327yhQRTYsNEWskACw</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>butik otel</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Pasaport Pier Istanbul</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>+90 216 450 22 23</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>https://istanbulpasaportpier.com/</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>566</v>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Otele telefonla ulaşmak imkansız (2023).</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=Pasaport%20Pier%20Istanbul&amp;query_place_id=ChIJU1bNmn65yhQRHc_TCkOpAr0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>emlak ofisi</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>SULUKULE GAYRİMENKUL</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>+90 549 353 05 51</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>http://www.sulukuleemlak.com/</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Telefona bakmıyor, geri dönmüyor (2023).</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=SULUKULE%20GAYR%C4%B0MENKUL&amp;query_place_id=ChIJHwz_MxS6yhQRRsC0j7gE34s</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n"/>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+      <c r="I25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Not</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Her sektörde sadece 12 işletme ve 8 anahtar kelime tarandı (bütçe sınırı). Sıfır çıkan sektörlerde ihtiyaç yok demek değildir; örneklem küçüktür. Sıralama yön göstericidir.</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n"/>
+      <c r="D26" s="3" t="n"/>
+      <c r="E26" s="3" t="n"/>
+      <c r="F26" s="3" t="n"/>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+      <c r="I26" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:O256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -18816,7 +19672,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
